--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="Rc02d5e2af5194e20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="R0d8a1d5280184519"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organigrama" sheetId="3" r:id="R845fd00cf0e74c7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="4" r:id="Rf5acf5af9faa47bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="5" r:id="R8498ded550ce4ed1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="Re35620877316426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="R237fc5719c714cb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organigrama" sheetId="3" r:id="R73a3883e8ad94c4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="4" r:id="R912de606f7504dc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="5" r:id="Rbeb3f49417264a65"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -362,7 +362,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Edita únicamente las celdas azules. El motor sólo muestra y contabiliza filas con Activo = Si. Para cada lanzamiento Peanuts, la fecha límite es un día antes.</x:v>
+        <x:v>Edita únicamente las celdas azules. El motor sólo muestra y contabiliza filas con Activo = Si. Peanuts se concentra en dos eventos y el encabezado Evidencia de Forms identifica cada evento.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -399,16 +399,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
-        <x:v>Rack FHW</x:v>
+        <x:v>Peanuts Charly&amp;Lucy</x:v>
       </x:c>
       <x:c r="C5" s="17" t="str">
-        <x:v>Validación de Rack FHW. Forms: Evidencia_Rack_FHW.</x:v>
+        <x:v>Anticipa materiales y artículos de Charly &amp; Lucy. Fecha límite: 20 Sep.</x:v>
       </x:c>
       <x:c r="D5" s="18" t="n">
         <x:v>46283.708333333336</x:v>
       </x:c>
       <x:c r="E5" s="18" t="n">
-        <x:v>46295.708333333336</x:v>
+        <x:v>46285.708333333336</x:v>
       </x:c>
       <x:c r="F5" s="21" t="str">
         <x:v>Si</x:v>
@@ -417,7 +417,7 @@
         <x:v>Si</x:v>
       </x:c>
       <x:c r="H5" s="21" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="I5" s="20" t="str">
         <x:f>IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente"))</x:f>
@@ -429,16 +429,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="17" t="str">
-        <x:v>Max &amp; Min</x:v>
+        <x:v>Peanuts Linus&amp;Snoopy</x:v>
       </x:c>
       <x:c r="C6" s="17" t="str">
-        <x:v>Estándar Max &amp; Min y acomodo de Back. Forms: Evidencia_Max&amp;Min.</x:v>
+        <x:v>Anticipa materiales y artículos de Linus &amp; Snoopy. Fecha límite: 27 Sep.</x:v>
       </x:c>
       <x:c r="D6" s="18" t="n">
         <x:v>46283.708333333336</x:v>
       </x:c>
       <x:c r="E6" s="18" t="n">
-        <x:v>46295.708333333336</x:v>
+        <x:v>46292.708333333336</x:v>
       </x:c>
       <x:c r="F6" s="21" t="str">
         <x:v>Si</x:v>
@@ -459,10 +459,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="17" t="str">
-        <x:v>Mandil Verde</x:v>
+        <x:v>Rack FHW</x:v>
       </x:c>
       <x:c r="C7" s="17" t="str">
-        <x:v>Seguimiento Mandil Verde. Forms: Evidencia_Mandil Verde.</x:v>
+        <x:v>Validación de Rack FHW. Forms: Evidencia_Rack_FHW.</x:v>
       </x:c>
       <x:c r="D7" s="18" t="n">
         <x:v>46283.708333333336</x:v>
@@ -489,10 +489,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="17" t="str">
-        <x:v>Lay Out</x:v>
+        <x:v>Max &amp; Min</x:v>
       </x:c>
       <x:c r="C8" s="17" t="str">
-        <x:v>Validación de estaciones y acomodo. Forms: Evidencia_Lay_Out.</x:v>
+        <x:v>Estándar Max &amp; Min y acomodo de Back. Forms: Evidencia_Max&amp;Min.</x:v>
       </x:c>
       <x:c r="D8" s="18" t="n">
         <x:v>46283.708333333336</x:v>
@@ -519,10 +519,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="17" t="str">
-        <x:v>Community Board</x:v>
+        <x:v>Mandil Verde</x:v>
       </x:c>
       <x:c r="C9" s="17" t="str">
-        <x:v>Validación de Community Board. Forms: ¿Cuentas con Community Board? + Evidencia_Community_Board.</x:v>
+        <x:v>Seguimiento Mandil Verde. Forms: Evidencia_Mandil Verde.</x:v>
       </x:c>
       <x:c r="D9" s="18" t="n">
         <x:v>46283.708333333336</x:v>
@@ -537,7 +537,7 @@
         <x:v>Si</x:v>
       </x:c>
       <x:c r="H9" s="21" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="I9" s="20" t="str">
         <x:f>IF(AND(D9&lt;&gt;"",TODAY()&lt;D9),"Programada",IF(AND(E9&lt;&gt;"",TODAY()&gt;E9),"Vencida","Vigente"))</x:f>
@@ -549,10 +549,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="17" t="str">
-        <x:v>Señaletica Back</x:v>
+        <x:v>Lay Out</x:v>
       </x:c>
       <x:c r="C10" s="17" t="str">
-        <x:v>Materiales actualizados en Back. Forms: Evidencia_Señaletica_Back.</x:v>
+        <x:v>Validación de estaciones y acomodo. Forms: Evidencia_Lay_Out.</x:v>
       </x:c>
       <x:c r="D10" s="18" t="n">
         <x:v>46283.708333333336</x:v>
@@ -567,7 +567,7 @@
         <x:v>Si</x:v>
       </x:c>
       <x:c r="H10" s="21" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="I10" s="20" t="str">
         <x:f>IF(AND(D10&lt;&gt;"",TODAY()&lt;D10),"Programada",IF(AND(E10&lt;&gt;"",TODAY()&gt;E10),"Vencida","Vigente"))</x:f>
@@ -579,10 +579,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="17" t="str">
-        <x:v>Señaletica Lobby</x:v>
+        <x:v>Community Board</x:v>
       </x:c>
       <x:c r="C11" s="17" t="str">
-        <x:v>Materiales actualizados en Lobby. Forms: Evidencia_Señaletica_Lobby.</x:v>
+        <x:v>Validación de Community Board. Forms: ¿Cuentas con Community Board? + Evidencia_Community_Board.</x:v>
       </x:c>
       <x:c r="D11" s="18" t="n">
         <x:v>46283.708333333336</x:v>
@@ -597,7 +597,7 @@
         <x:v>Si</x:v>
       </x:c>
       <x:c r="H11" s="21" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="I11" s="20" t="str">
         <x:f>IF(AND(D11&lt;&gt;"",TODAY()&lt;D11),"Programada",IF(AND(E11&lt;&gt;"",TODAY()&gt;E11),"Vencida","Vigente"))</x:f>
@@ -609,10 +609,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="17" t="str">
-        <x:v>Jarras Blender | Cold Foam</x:v>
+        <x:v>Señaletica Back</x:v>
       </x:c>
       <x:c r="C12" s="17" t="str">
-        <x:v>Jarras completas, sin daños y listas para operar. Forms: Jarra Blender + Jarras Cold Foam + Evidencia_Jarras_Blender_&amp;_Cold_Foam.</x:v>
+        <x:v>Materiales actualizados en Back. Forms: Evidencia_Señaletica_Back.</x:v>
       </x:c>
       <x:c r="D12" s="18" t="n">
         <x:v>46283.708333333336</x:v>
@@ -627,7 +627,7 @@
         <x:v>Si</x:v>
       </x:c>
       <x:c r="H12" s="21" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="I12" s="20" t="str">
         <x:f>IF(AND(D12&lt;&gt;"",TODAY()&lt;D12),"Programada",IF(AND(E12&lt;&gt;"",TODAY()&gt;E12),"Vencida","Vigente"))</x:f>
@@ -639,16 +639,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
-        <x:v>Peanuts Charly | 21 Sep</x:v>
+        <x:v>Señaletica Lobby</x:v>
       </x:c>
       <x:c r="C13" s="17" t="str">
-        <x:v>Anticipa materiales y artículos de Charly. Forms: Evidencia_Peanuts_Charly_21Sep. Lanzamiento 21 Sep; límite 20 Sep.</x:v>
+        <x:v>Materiales actualizados en Lobby. Forms: Evidencia_Señaletica_Lobby.</x:v>
       </x:c>
       <x:c r="D13" s="18" t="n">
         <x:v>46283.708333333336</x:v>
       </x:c>
       <x:c r="E13" s="18" t="n">
-        <x:v>46285.708333333336</x:v>
+        <x:v>46295.708333333336</x:v>
       </x:c>
       <x:c r="F13" s="21" t="str">
         <x:v>Si</x:v>
@@ -657,7 +657,7 @@
         <x:v>Si</x:v>
       </x:c>
       <x:c r="H13" s="21" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="I13" s="20" t="str">
         <x:f>IF(AND(D13&lt;&gt;"",TODAY()&lt;D13),"Programada",IF(AND(E13&lt;&gt;"",TODAY()&gt;E13),"Vencida","Vigente"))</x:f>
@@ -669,16 +669,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>Peanuts Lucy | 24 Sep</x:v>
+        <x:v>Jarras Blender | Cold Foam</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
-        <x:v>Anticipa materiales y artículos de Lucy. Forms: Evidencia_Peanuts_Lucy_24Sep. Lanzamiento 24 Sep; límite 23 Sep.</x:v>
+        <x:v>Jarras completas, sin daños y listas para operar. Forms: Jarra Blender + Jarras Cold Foam + Evidencia_Jarras_Blender_&amp;_Cold_Foam.</x:v>
       </x:c>
       <x:c r="D14" s="18" t="n">
         <x:v>46283.708333333336</x:v>
       </x:c>
       <x:c r="E14" s="18" t="n">
-        <x:v>46288.708333333336</x:v>
+        <x:v>46295.708333333336</x:v>
       </x:c>
       <x:c r="F14" s="21" t="str">
         <x:v>Si</x:v>
@@ -695,71 +695,71 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
-      <x:c r="A15" s="21" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B15" s="17" t="str">
-        <x:v>Peanuts Linus | 28 Sep</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="str">
-        <x:v>Anticipa materiales y artículos de Linus. Forms: Evidencia_Peanuts_Linus_28Sep. Lanzamiento 28 Sep; límite 27 Sep.</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="n">
-        <x:v>46283.708333333336</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="n">
-        <x:v>46292.708333333336</x:v>
-      </x:c>
-      <x:c r="F15" s="21" t="str">
-        <x:v>Si</x:v>
-      </x:c>
-      <x:c r="G15" s="21" t="str">
-        <x:v>Si</x:v>
-      </x:c>
-      <x:c r="H15" s="21" t="str">
-        <x:v>Alta</x:v>
+      <x:c r="A15" s="22" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
+        <x:v>Roll Out</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>Histórico; no se muestra ni se contabiliza.</x:v>
+      </x:c>
+      <x:c r="D15" s="19" t="n">
+        <x:v>46262.708333333336</x:v>
+      </x:c>
+      <x:c r="E15" s="19" t="n">
+        <x:v>46268.708333333336</x:v>
+      </x:c>
+      <x:c r="F15" s="22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G15" s="22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="H15" s="22" t="str">
+        <x:v>Baja</x:v>
       </x:c>
       <x:c r="I15" s="20" t="str">
         <x:f>IF(AND(D15&lt;&gt;"",TODAY()&lt;D15),"Programada",IF(AND(E15&lt;&gt;"",TODAY()&gt;E15),"Vencida","Vigente"))</x:f>
-        <x:v>Programada</x:v>
+        <x:v>Vencida</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
-      <x:c r="A16" s="21" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B16" s="17" t="str">
-        <x:v>Peanuts Snoopy | 2 Oct</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="str">
-        <x:v>Anticipa materiales y artículos de Snoopy. Forms: Evidencia_Peanuts_Snoopy_2Oct. Lanzamiento 2 Oct; límite 1 Oct.</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="n">
-        <x:v>46283.708333333336</x:v>
-      </x:c>
-      <x:c r="E16" s="18" t="n">
-        <x:v>46296.708333333336</x:v>
-      </x:c>
-      <x:c r="F16" s="21" t="str">
-        <x:v>Si</x:v>
-      </x:c>
-      <x:c r="G16" s="21" t="str">
-        <x:v>Si</x:v>
-      </x:c>
-      <x:c r="H16" s="21" t="str">
-        <x:v>Alta</x:v>
+      <x:c r="A16" s="22" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>Programacion Hornos Merry - Focaccia</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="str">
+        <x:v>Histórico; no se muestra ni se contabiliza.</x:v>
+      </x:c>
+      <x:c r="D16" s="19" t="n">
+        <x:v>46262.708333333336</x:v>
+      </x:c>
+      <x:c r="E16" s="19" t="n">
+        <x:v>46280.708333333336</x:v>
+      </x:c>
+      <x:c r="F16" s="22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G16" s="22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="H16" s="22" t="str">
+        <x:v>Baja</x:v>
       </x:c>
       <x:c r="I16" s="20" t="str">
         <x:f>IF(AND(D16&lt;&gt;"",TODAY()&lt;D16),"Programada",IF(AND(E16&lt;&gt;"",TODAY()&gt;E16),"Vencida","Vigente"))</x:f>
-        <x:v>Programada</x:v>
+        <x:v>Vencida</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
       <x:c r="A17" s="22" t="n">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B17" s="16" t="str">
-        <x:v>Roll Out</x:v>
+        <x:v>Fotografia - SM</x:v>
       </x:c>
       <x:c r="C17" s="16" t="str">
         <x:v>Histórico; no se muestra ni se contabiliza.</x:v>
@@ -768,7 +768,7 @@
         <x:v>46262.708333333336</x:v>
       </x:c>
       <x:c r="E17" s="19" t="n">
-        <x:v>46268.708333333336</x:v>
+        <x:v>46271.708333333336</x:v>
       </x:c>
       <x:c r="F17" s="22" t="str">
         <x:v>No</x:v>
@@ -786,10 +786,10 @@
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
       <x:c r="A18" s="22" t="n">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B18" s="16" t="str">
-        <x:v>Programacion Hornos Merry - Focaccia</x:v>
+        <x:v>Activacion PSL Sharpie</x:v>
       </x:c>
       <x:c r="C18" s="16" t="str">
         <x:v>Histórico; no se muestra ni se contabiliza.</x:v>
@@ -798,7 +798,7 @@
         <x:v>46262.708333333336</x:v>
       </x:c>
       <x:c r="E18" s="19" t="n">
-        <x:v>46280.708333333336</x:v>
+        <x:v>46265.708333333336</x:v>
       </x:c>
       <x:c r="F18" s="22" t="str">
         <x:v>No</x:v>
@@ -816,19 +816,19 @@
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
       <x:c r="A19" s="22" t="n">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B19" s="16" t="str">
-        <x:v>Fotografia - SM</x:v>
+        <x:v>Validacion Horario Festivo Sep 26</x:v>
       </x:c>
       <x:c r="C19" s="16" t="str">
         <x:v>Histórico; no se muestra ni se contabiliza.</x:v>
       </x:c>
       <x:c r="D19" s="19" t="n">
-        <x:v>46262.708333333336</x:v>
+        <x:v>46278.708333333336</x:v>
       </x:c>
       <x:c r="E19" s="19" t="n">
-        <x:v>46271.708333333336</x:v>
+        <x:v>46280.708333333336</x:v>
       </x:c>
       <x:c r="F19" s="22" t="str">
         <x:v>No</x:v>
@@ -841,66 +841,6 @@
       </x:c>
       <x:c r="I19" s="20" t="str">
         <x:f>IF(AND(D19&lt;&gt;"",TODAY()&lt;D19),"Programada",IF(AND(E19&lt;&gt;"",TODAY()&gt;E19),"Vencida","Vigente"))</x:f>
-        <x:v>Vencida</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="34" customHeight="1">
-      <x:c r="A20" s="22" t="n">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B20" s="16" t="str">
-        <x:v>Activacion PSL Sharpie</x:v>
-      </x:c>
-      <x:c r="C20" s="16" t="str">
-        <x:v>Histórico; no se muestra ni se contabiliza.</x:v>
-      </x:c>
-      <x:c r="D20" s="19" t="n">
-        <x:v>46262.708333333336</x:v>
-      </x:c>
-      <x:c r="E20" s="19" t="n">
-        <x:v>46265.708333333336</x:v>
-      </x:c>
-      <x:c r="F20" s="22" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="G20" s="22" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H20" s="22" t="str">
-        <x:v>Baja</x:v>
-      </x:c>
-      <x:c r="I20" s="20" t="str">
-        <x:f>IF(AND(D20&lt;&gt;"",TODAY()&lt;D20),"Programada",IF(AND(E20&lt;&gt;"",TODAY()&gt;E20),"Vencida","Vigente"))</x:f>
-        <x:v>Vencida</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="34" customHeight="1">
-      <x:c r="A21" s="22" t="n">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B21" s="16" t="str">
-        <x:v>Validacion Horario Festivo Sep 26</x:v>
-      </x:c>
-      <x:c r="C21" s="16" t="str">
-        <x:v>Histórico; no se muestra ni se contabiliza.</x:v>
-      </x:c>
-      <x:c r="D21" s="19" t="n">
-        <x:v>46278.708333333336</x:v>
-      </x:c>
-      <x:c r="E21" s="19" t="n">
-        <x:v>46280.708333333336</x:v>
-      </x:c>
-      <x:c r="F21" s="22" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="G21" s="22" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H21" s="22" t="str">
-        <x:v>Baja</x:v>
-      </x:c>
-      <x:c r="I21" s="20" t="str">
-        <x:f>IF(AND(D21&lt;&gt;"",TODAY()&lt;D21),"Programada",IF(AND(E21&lt;&gt;"",TODAY()&gt;E21),"Vencida","Vigente"))</x:f>
         <x:v>Vencida</x:v>
       </x:c>
     </x:row>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="Re35620877316426e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="R237fc5719c714cb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organigrama" sheetId="3" r:id="R73a3883e8ad94c4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="4" r:id="R912de606f7504dc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="5" r:id="Rbeb3f49417264a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="R76d660184c7b417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="R8f5ac2d8835b477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organigrama" sheetId="3" r:id="R14fa74cff2e34f35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="4" r:id="Rcae9012e93c946e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="5" r:id="R35c40325ae9c4c9f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -362,7 +362,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Edita únicamente las celdas azules. El motor sólo muestra y contabiliza filas con Activo = Si. Peanuts se concentra en dos eventos y el encabezado Evidencia de Forms identifica cada evento.</x:v>
+        <x:v>Edita únicamente las celdas azules. El corte histórico conserva el avance y el Forms actual suma cualquier actividad con Activo = Si. El encabezado Evidencia identifica cada evento.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DA67D8-FDB0-46E7-A7F9-40157239BAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9291BB34-AA11-4439-907D-556E5A767367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="909">
   <si>
     <t>CMS · Actividades vigentes y fechas</t>
   </si>
@@ -2758,6 +2758,12 @@
   </si>
   <si>
     <t>Registra y evidencia jarras completas, sin daños y listas para operar.</t>
+  </si>
+  <si>
+    <t>Organizacion Refrigeradores Back</t>
+  </si>
+  <si>
+    <t>Valida el acomodo de refrigeradores de Back y optimiza espacios</t>
   </si>
 </sst>
 </file>
@@ -3088,12 +3094,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="67" customWidth="1"/>
+    <col min="3" max="3" width="54.4140625" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
@@ -3181,8 +3187,8 @@
         <v>13</v>
       </c>
       <c r="I5" s="6" t="str">
-        <f t="shared" ref="I5:I19" ca="1" si="0">IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente"))</f>
-        <v>Programada</v>
+        <f t="shared" ref="I5:I20" ca="1" si="0">IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente"))</f>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="34" customHeight="1">
@@ -3212,7 +3218,7 @@
       </c>
       <c r="I6" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Programada</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="34" customHeight="1">
@@ -3242,7 +3248,7 @@
       </c>
       <c r="I7" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Programada</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="34" customHeight="1">
@@ -3272,7 +3278,7 @@
       </c>
       <c r="I8" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Programada</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="34" customHeight="1">
@@ -3302,7 +3308,7 @@
       </c>
       <c r="I9" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Programada</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="34" customHeight="1">
@@ -3332,7 +3338,7 @@
       </c>
       <c r="I10" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Programada</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="34" customHeight="1">
@@ -3362,7 +3368,7 @@
       </c>
       <c r="I11" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Programada</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="34" customHeight="1">
@@ -3392,7 +3398,7 @@
       </c>
       <c r="I12" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Programada</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="34" customHeight="1">
@@ -3422,7 +3428,7 @@
       </c>
       <c r="I13" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Programada</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="34" customHeight="1">
@@ -3452,45 +3458,45 @@
       </c>
       <c r="I14" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Programada</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="34" customHeight="1">
-      <c r="A15" s="8">
-        <v>90</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="5">
-        <v>46262.708333333336</v>
-      </c>
-      <c r="E15" s="5">
-        <v>46268.708333333336</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>27</v>
+      <c r="A15" s="7">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46283.708333333336</v>
+      </c>
+      <c r="E15" s="4">
+        <v>46295.708333333336</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="I15" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Vencida</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="34" customHeight="1">
       <c r="A16" s="8">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>25</v>
@@ -3499,7 +3505,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E16" s="5">
-        <v>46280.708333333336</v>
+        <v>46268.708333333336</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>26</v>
@@ -3517,10 +3523,10 @@
     </row>
     <row r="17" spans="1:9" ht="34" customHeight="1">
       <c r="A17" s="8">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>25</v>
@@ -3529,7 +3535,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E17" s="5">
-        <v>46271.708333333336</v>
+        <v>46280.708333333336</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>26</v>
@@ -3547,10 +3553,10 @@
     </row>
     <row r="18" spans="1:9" ht="34" customHeight="1">
       <c r="A18" s="8">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
@@ -3559,7 +3565,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E18" s="5">
-        <v>46265.708333333336</v>
+        <v>46271.708333333336</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>26</v>
@@ -3577,19 +3583,19 @@
     </row>
     <row r="19" spans="1:9" ht="34" customHeight="1">
       <c r="A19" s="8">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="5">
-        <v>46278.708333333336</v>
+        <v>46262.708333333336</v>
       </c>
       <c r="E19" s="5">
-        <v>46280.708333333336</v>
+        <v>46265.708333333336</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>26</v>
@@ -3601,6 +3607,36 @@
         <v>27</v>
       </c>
       <c r="I19" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Vencida</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="34" customHeight="1">
+      <c r="A20" s="8">
+        <v>94</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46278.708333333336</v>
+      </c>
+      <c r="E20" s="5">
+        <v>46280.708333333336</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Vencida</v>
       </c>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC9B428-5103-4CA8-92FE-4FA07858B912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDEFF5B-39C4-4D4B-B382-9BB7DB9C49E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3310,10 +3310,10 @@
         <v>46295.708333333336</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>17</v>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDEFF5B-39C4-4D4B-B382-9BB7DB9C49E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40A285A-85F2-49DA-B68E-38C036536DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="911">
   <si>
     <t>CMS · Actividades vigentes y fechas</t>
   </si>
@@ -2764,6 +2764,12 @@
   </si>
   <si>
     <t>Valida con DM cada Lay Out</t>
+  </si>
+  <si>
+    <t>Va X Cuenta</t>
+  </si>
+  <si>
+    <t>Valida Donativos Va x Cuenta por plantilla</t>
   </si>
 </sst>
 </file>
@@ -3154,7 +3160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3259,7 +3265,7 @@
         <v>36</v>
       </c>
       <c r="I5" s="11" t="str">
-        <f t="shared" ref="I5:I20" ca="1" si="0">IF(B5="","",IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente")))</f>
+        <f t="shared" ref="I5:I21" ca="1" si="0">IF(B5="","",IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente")))</f>
         <v>Vencida</v>
       </c>
     </row>
@@ -3280,10 +3286,10 @@
         <v>46292.708333333336</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>13</v>
@@ -3565,40 +3571,40 @@
     </row>
     <row r="16" spans="1:9" ht="23" customHeight="1">
       <c r="A16" s="5">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>33</v>
+        <v>909</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>34</v>
+        <v>910</v>
       </c>
       <c r="D16" s="10">
-        <v>46262.708333333336</v>
+        <v>46283.708333333336</v>
       </c>
       <c r="E16" s="10">
-        <v>46268.708333333336</v>
+        <v>46295.708333333336</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I16" s="11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Vencida</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="23" customHeight="1">
       <c r="A17" s="5">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>34</v>
@@ -3607,7 +3613,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E17" s="10">
-        <v>46280.708333333336</v>
+        <v>46268.708333333336</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>35</v>
@@ -3625,10 +3631,10 @@
     </row>
     <row r="18" spans="1:9" ht="23" customHeight="1">
       <c r="A18" s="5">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>34</v>
@@ -3637,7 +3643,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E18" s="10">
-        <v>46271.708333333336</v>
+        <v>46280.708333333336</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>35</v>
@@ -3655,10 +3661,10 @@
     </row>
     <row r="19" spans="1:9" ht="23" customHeight="1">
       <c r="A19" s="5">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>34</v>
@@ -3667,7 +3673,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E19" s="10">
-        <v>46265.708333333336</v>
+        <v>46271.708333333336</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>35</v>
@@ -3685,19 +3691,19 @@
     </row>
     <row r="20" spans="1:9" ht="23" customHeight="1">
       <c r="A20" s="5">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="10">
-        <v>46278.708333333336</v>
+        <v>46262.708333333336</v>
       </c>
       <c r="E20" s="10">
-        <v>46280.708333333336</v>
+        <v>46265.708333333336</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>35</v>
@@ -3714,17 +3720,33 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="23" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="12" t="str">
-        <f t="shared" ref="I21:I40" ca="1" si="1">IF(B21="","",IF(AND(D21&lt;&gt;"",TODAY()&lt;D21),"Programada",IF(AND(E21&lt;&gt;"",TODAY()&gt;E21),"Vencida","Vigente")))</f>
-        <v/>
+      <c r="A21" s="5">
+        <v>94</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="10">
+        <v>46278.708333333336</v>
+      </c>
+      <c r="E21" s="10">
+        <v>46280.708333333336</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="11" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Vencida</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="23" customHeight="1">
@@ -3737,7 +3759,7 @@
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ref="I22:I41" ca="1" si="1">IF(B22="","",IF(AND(D22&lt;&gt;"",TODAY()&lt;D22),"Programada",IF(AND(E22&lt;&gt;"",TODAY()&gt;E22),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3993,16 +4015,30 @@
         <v/>
       </c>
     </row>
+    <row r="41" spans="1:9" ht="23" customHeight="1">
+      <c r="A41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="12" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:G40" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="F5:G41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Si,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H5:H40" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="H5:H41" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40A285A-85F2-49DA-B68E-38C036536DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B4C947-C27A-443F-91BB-52607718AA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3168,7 +3168,7 @@
     <col min="3" max="3" width="58" customWidth="1"/>
     <col min="4" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="7" max="7" width="14.25" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
@@ -3244,16 +3244,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D5" s="10">
         <v>46283.708333333336</v>
       </c>
       <c r="E5" s="10">
-        <v>46285.708333333336</v>
+        <v>46295.708333333336</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>35</v>
@@ -3262,11 +3262,11 @@
         <v>35</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I5" s="11" t="str">
-        <f t="shared" ref="I5:I21" ca="1" si="0">IF(B5="","",IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente")))</f>
-        <v>Vencida</v>
+        <f ca="1">IF(B5="","",IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente")))</f>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="23" customHeight="1">
@@ -3274,28 +3274,28 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D6" s="10">
         <v>46283.708333333336</v>
       </c>
       <c r="E6" s="10">
-        <v>46292.708333333336</v>
+        <v>46295.708333333336</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I6" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B6="","",IF(AND(D6&lt;&gt;"",TODAY()&lt;D6),"Programada",IF(AND(E6&lt;&gt;"",TODAY()&gt;E6),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -3304,10 +3304,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D7" s="10">
         <v>46283.708333333336</v>
@@ -3316,16 +3316,16 @@
         <v>46295.708333333336</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B7="","",IF(AND(D7&lt;&gt;"",TODAY()&lt;D7),"Programada",IF(AND(E7&lt;&gt;"",TODAY()&gt;E7),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -3334,10 +3334,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>19</v>
+        <v>908</v>
       </c>
       <c r="D8" s="10">
         <v>46283.708333333336</v>
@@ -3355,7 +3355,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B8="","",IF(AND(D8&lt;&gt;"",TODAY()&lt;D8),"Programada",IF(AND(E8&lt;&gt;"",TODAY()&gt;E8),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -3364,10 +3364,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" s="10">
         <v>46283.708333333336</v>
@@ -3382,10 +3382,10 @@
         <v>12</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I9" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B9="","",IF(AND(D9&lt;&gt;"",TODAY()&lt;D9),"Programada",IF(AND(E9&lt;&gt;"",TODAY()&gt;E9),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -3394,10 +3394,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>908</v>
+        <v>26</v>
       </c>
       <c r="D10" s="10">
         <v>46283.708333333336</v>
@@ -3412,10 +3412,10 @@
         <v>12</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I10" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B10="","",IF(AND(D10&lt;&gt;"",TODAY()&lt;D10),"Programada",IF(AND(E10&lt;&gt;"",TODAY()&gt;E10),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -3424,10 +3424,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D11" s="10">
         <v>46283.708333333336</v>
@@ -3442,10 +3442,10 @@
         <v>12</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I11" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B11="","",IF(AND(D11&lt;&gt;"",TODAY()&lt;D11),"Programada",IF(AND(E11&lt;&gt;"",TODAY()&gt;E11),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -3454,10 +3454,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12" s="10">
         <v>46283.708333333336</v>
@@ -3472,10 +3472,10 @@
         <v>12</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I12" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B12="","",IF(AND(D12&lt;&gt;"",TODAY()&lt;D12),"Programada",IF(AND(E12&lt;&gt;"",TODAY()&gt;E12),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -3484,10 +3484,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13" s="10">
         <v>46283.708333333336</v>
@@ -3502,10 +3502,10 @@
         <v>12</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I13" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B13="","",IF(AND(D13&lt;&gt;"",TODAY()&lt;D13),"Programada",IF(AND(E13&lt;&gt;"",TODAY()&gt;E13),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -3514,10 +3514,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>29</v>
+        <v>909</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>30</v>
+        <v>910</v>
       </c>
       <c r="D14" s="10">
         <v>46283.708333333336</v>
@@ -3535,76 +3535,76 @@
         <v>13</v>
       </c>
       <c r="I14" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B14="","",IF(AND(D14&lt;&gt;"",TODAY()&lt;D14),"Programada",IF(AND(E14&lt;&gt;"",TODAY()&gt;E14),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="23" customHeight="1">
       <c r="A15" s="5">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" s="10">
-        <v>46283.708333333336</v>
+        <v>46262.708333333336</v>
       </c>
       <c r="E15" s="10">
-        <v>46295.708333333336</v>
+        <v>46268.708333333336</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I15" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Vigente</v>
+        <f ca="1">IF(B15="","",IF(AND(D15&lt;&gt;"",TODAY()&lt;D15),"Programada",IF(AND(E15&lt;&gt;"",TODAY()&gt;E15),"Vencida","Vigente")))</f>
+        <v>Vencida</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="23" customHeight="1">
       <c r="A16" s="5">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>909</v>
+        <v>37</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>910</v>
+        <v>34</v>
       </c>
       <c r="D16" s="10">
-        <v>46283.708333333336</v>
+        <v>46262.708333333336</v>
       </c>
       <c r="E16" s="10">
-        <v>46295.708333333336</v>
+        <v>46280.708333333336</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I16" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Vigente</v>
+        <f ca="1">IF(B16="","",IF(AND(D16&lt;&gt;"",TODAY()&lt;D16),"Programada",IF(AND(E16&lt;&gt;"",TODAY()&gt;E16),"Vencida","Vigente")))</f>
+        <v>Vencida</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="23" customHeight="1">
       <c r="A17" s="5">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>34</v>
@@ -3613,7 +3613,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E17" s="10">
-        <v>46268.708333333336</v>
+        <v>46271.708333333336</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>35</v>
@@ -3625,16 +3625,16 @@
         <v>36</v>
       </c>
       <c r="I17" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B17="","",IF(AND(D17&lt;&gt;"",TODAY()&lt;D17),"Programada",IF(AND(E17&lt;&gt;"",TODAY()&gt;E17),"Vencida","Vigente")))</f>
         <v>Vencida</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="23" customHeight="1">
       <c r="A18" s="5">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>34</v>
@@ -3643,7 +3643,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E18" s="10">
-        <v>46280.708333333336</v>
+        <v>46265.708333333336</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>35</v>
@@ -3655,25 +3655,25 @@
         <v>36</v>
       </c>
       <c r="I18" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B18="","",IF(AND(D18&lt;&gt;"",TODAY()&lt;D18),"Programada",IF(AND(E18&lt;&gt;"",TODAY()&gt;E18),"Vencida","Vigente")))</f>
         <v>Vencida</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="23" customHeight="1">
       <c r="A19" s="5">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="10">
-        <v>46262.708333333336</v>
+        <v>46278.708333333336</v>
       </c>
       <c r="E19" s="10">
-        <v>46271.708333333336</v>
+        <v>46280.708333333336</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>35</v>
@@ -3685,25 +3685,25 @@
         <v>36</v>
       </c>
       <c r="I19" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B19="","",IF(AND(D19&lt;&gt;"",TODAY()&lt;D19),"Programada",IF(AND(E19&lt;&gt;"",TODAY()&gt;E19),"Vencida","Vigente")))</f>
         <v>Vencida</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="23" customHeight="1">
       <c r="A20" s="5">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D20" s="10">
-        <v>46262.708333333336</v>
+        <v>46283.708333333336</v>
       </c>
       <c r="E20" s="10">
-        <v>46265.708333333336</v>
+        <v>46285.708333333336</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>35</v>
@@ -3715,25 +3715,25 @@
         <v>36</v>
       </c>
       <c r="I20" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(B20="","",IF(AND(D20&lt;&gt;"",TODAY()&lt;D20),"Programada",IF(AND(E20&lt;&gt;"",TODAY()&gt;E20),"Vencida","Vigente")))</f>
         <v>Vencida</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="23" customHeight="1">
       <c r="A21" s="5">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D21" s="10">
-        <v>46278.708333333336</v>
+        <v>46283.708333333336</v>
       </c>
       <c r="E21" s="10">
-        <v>46280.708333333336</v>
+        <v>46292.708333333336</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>35</v>
@@ -3742,11 +3742,11 @@
         <v>35</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I21" s="11" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Vencida</v>
+        <f ca="1">IF(B21="","",IF(AND(D21&lt;&gt;"",TODAY()&lt;D21),"Programada",IF(AND(E21&lt;&gt;"",TODAY()&gt;E21),"Vencida","Vigente")))</f>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="23" customHeight="1">
@@ -3759,7 +3759,7 @@
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="12" t="str">
-        <f t="shared" ref="I22:I41" ca="1" si="1">IF(B22="","",IF(AND(D22&lt;&gt;"",TODAY()&lt;D22),"Programada",IF(AND(E22&lt;&gt;"",TODAY()&gt;E22),"Vencida","Vigente")))</f>
+        <f ca="1">IF(B22="","",IF(AND(D22&lt;&gt;"",TODAY()&lt;D22),"Programada",IF(AND(E22&lt;&gt;"",TODAY()&gt;E22),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B23="","",IF(AND(D23&lt;&gt;"",TODAY()&lt;D23),"Programada",IF(AND(E23&lt;&gt;"",TODAY()&gt;E23),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B24="","",IF(AND(D24&lt;&gt;"",TODAY()&lt;D24),"Programada",IF(AND(E24&lt;&gt;"",TODAY()&gt;E24),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B25="","",IF(AND(D25&lt;&gt;"",TODAY()&lt;D25),"Programada",IF(AND(E25&lt;&gt;"",TODAY()&gt;E25),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B26="","",IF(AND(D26&lt;&gt;"",TODAY()&lt;D26),"Programada",IF(AND(E26&lt;&gt;"",TODAY()&gt;E26),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B27="","",IF(AND(D27&lt;&gt;"",TODAY()&lt;D27),"Programada",IF(AND(E27&lt;&gt;"",TODAY()&gt;E27),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B28="","",IF(AND(D28&lt;&gt;"",TODAY()&lt;D28),"Programada",IF(AND(E28&lt;&gt;"",TODAY()&gt;E28),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B29="","",IF(AND(D29&lt;&gt;"",TODAY()&lt;D29),"Programada",IF(AND(E29&lt;&gt;"",TODAY()&gt;E29),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B30="","",IF(AND(D30&lt;&gt;"",TODAY()&lt;D30),"Programada",IF(AND(E30&lt;&gt;"",TODAY()&gt;E30),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B31="","",IF(AND(D31&lt;&gt;"",TODAY()&lt;D31),"Programada",IF(AND(E31&lt;&gt;"",TODAY()&gt;E31),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3899,7 +3899,7 @@
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B32="","",IF(AND(D32&lt;&gt;"",TODAY()&lt;D32),"Programada",IF(AND(E32&lt;&gt;"",TODAY()&gt;E32),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B33="","",IF(AND(D33&lt;&gt;"",TODAY()&lt;D33),"Programada",IF(AND(E33&lt;&gt;"",TODAY()&gt;E33),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B34="","",IF(AND(D34&lt;&gt;"",TODAY()&lt;D34),"Programada",IF(AND(E34&lt;&gt;"",TODAY()&gt;E34),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B35="","",IF(AND(D35&lt;&gt;"",TODAY()&lt;D35),"Programada",IF(AND(E35&lt;&gt;"",TODAY()&gt;E35),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B36="","",IF(AND(D36&lt;&gt;"",TODAY()&lt;D36),"Programada",IF(AND(E36&lt;&gt;"",TODAY()&gt;E36),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B37="","",IF(AND(D37&lt;&gt;"",TODAY()&lt;D37),"Programada",IF(AND(E37&lt;&gt;"",TODAY()&gt;E37),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B38="","",IF(AND(D38&lt;&gt;"",TODAY()&lt;D38),"Programada",IF(AND(E38&lt;&gt;"",TODAY()&gt;E38),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B39="","",IF(AND(D39&lt;&gt;"",TODAY()&lt;D39),"Programada",IF(AND(E39&lt;&gt;"",TODAY()&gt;E39),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B40="","",IF(AND(D40&lt;&gt;"",TODAY()&lt;D40),"Programada",IF(AND(E40&lt;&gt;"",TODAY()&gt;E40),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
@@ -4025,11 +4025,14 @@
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF(B41="","",IF(AND(D41&lt;&gt;"",TODAY()&lt;D41),"Programada",IF(AND(E41&lt;&gt;"",TODAY()&gt;E41),"Vencida","Vigente")))</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:I41">
+    <sortCondition ref="A4:A41"/>
+  </sortState>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B4C947-C27A-443F-91BB-52607718AA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2F6088-ED10-4CF5-A6B8-42B140F6D6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="913">
   <si>
     <t>CMS · Actividades vigentes y fechas</t>
   </si>
@@ -2770,6 +2770,12 @@
   </si>
   <si>
     <t>Valida Donativos Va x Cuenta por plantilla</t>
+  </si>
+  <si>
+    <t>FHW</t>
+  </si>
+  <si>
+    <t>Valida Insumos  FHW Cubiertos &amp; Taza 3 Oz</t>
   </si>
 </sst>
 </file>
@@ -3160,7 +3166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3253,7 +3259,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E5" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>35</v>
@@ -3265,7 +3271,7 @@
         <v>17</v>
       </c>
       <c r="I5" s="11" t="str">
-        <f ca="1">IF(B5="","",IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente")))</f>
+        <f t="shared" ref="I5:I42" ca="1" si="0">IF(B5="","",IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente")))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -3283,7 +3289,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E6" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>12</v>
@@ -3295,7 +3301,7 @@
         <v>13</v>
       </c>
       <c r="I6" s="11" t="str">
-        <f ca="1">IF(B6="","",IF(AND(D6&lt;&gt;"",TODAY()&lt;D6),"Programada",IF(AND(E6&lt;&gt;"",TODAY()&gt;E6),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
       </c>
     </row>
@@ -3313,7 +3319,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E7" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>12</v>
@@ -3325,7 +3331,7 @@
         <v>17</v>
       </c>
       <c r="I7" s="11" t="str">
-        <f ca="1">IF(B7="","",IF(AND(D7&lt;&gt;"",TODAY()&lt;D7),"Programada",IF(AND(E7&lt;&gt;"",TODAY()&gt;E7),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
       </c>
     </row>
@@ -3343,7 +3349,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E8" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>12</v>
@@ -3355,7 +3361,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="11" t="str">
-        <f ca="1">IF(B8="","",IF(AND(D8&lt;&gt;"",TODAY()&lt;D8),"Programada",IF(AND(E8&lt;&gt;"",TODAY()&gt;E8),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
       </c>
     </row>
@@ -3373,7 +3379,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E9" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>12</v>
@@ -3385,7 +3391,7 @@
         <v>13</v>
       </c>
       <c r="I9" s="11" t="str">
-        <f ca="1">IF(B9="","",IF(AND(D9&lt;&gt;"",TODAY()&lt;D9),"Programada",IF(AND(E9&lt;&gt;"",TODAY()&gt;E9),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
       </c>
     </row>
@@ -3403,7 +3409,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E10" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>12</v>
@@ -3415,7 +3421,7 @@
         <v>17</v>
       </c>
       <c r="I10" s="11" t="str">
-        <f ca="1">IF(B10="","",IF(AND(D10&lt;&gt;"",TODAY()&lt;D10),"Programada",IF(AND(E10&lt;&gt;"",TODAY()&gt;E10),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
       </c>
     </row>
@@ -3433,7 +3439,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E11" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>12</v>
@@ -3445,7 +3451,7 @@
         <v>17</v>
       </c>
       <c r="I11" s="11" t="str">
-        <f ca="1">IF(B11="","",IF(AND(D11&lt;&gt;"",TODAY()&lt;D11),"Programada",IF(AND(E11&lt;&gt;"",TODAY()&gt;E11),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
       </c>
     </row>
@@ -3463,7 +3469,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E12" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>12</v>
@@ -3475,7 +3481,7 @@
         <v>13</v>
       </c>
       <c r="I12" s="11" t="str">
-        <f ca="1">IF(B12="","",IF(AND(D12&lt;&gt;"",TODAY()&lt;D12),"Programada",IF(AND(E12&lt;&gt;"",TODAY()&gt;E12),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
       </c>
     </row>
@@ -3493,7 +3499,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E13" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>12</v>
@@ -3505,7 +3511,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="11" t="str">
-        <f ca="1">IF(B13="","",IF(AND(D13&lt;&gt;"",TODAY()&lt;D13),"Programada",IF(AND(E13&lt;&gt;"",TODAY()&gt;E13),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
       </c>
     </row>
@@ -3523,58 +3529,58 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E14" s="10">
-        <v>46295.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I14" s="11" t="str">
-        <f ca="1">IF(B14="","",IF(AND(D14&lt;&gt;"",TODAY()&lt;D14),"Programada",IF(AND(E14&lt;&gt;"",TODAY()&gt;E14),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="23" customHeight="1">
       <c r="A15" s="5">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>33</v>
+        <v>911</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>34</v>
+        <v>912</v>
       </c>
       <c r="D15" s="10">
-        <v>46262.708333333336</v>
+        <v>46283.708333333336</v>
       </c>
       <c r="E15" s="10">
-        <v>46268.708333333336</v>
+        <v>46300.708333333336</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I15" s="11" t="str">
-        <f ca="1">IF(B15="","",IF(AND(D15&lt;&gt;"",TODAY()&lt;D15),"Programada",IF(AND(E15&lt;&gt;"",TODAY()&gt;E15),"Vencida","Vigente")))</f>
-        <v>Vencida</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="23" customHeight="1">
       <c r="A16" s="5">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>34</v>
@@ -3583,7 +3589,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E16" s="10">
-        <v>46280.708333333336</v>
+        <v>46268.708333333336</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>35</v>
@@ -3595,16 +3601,16 @@
         <v>36</v>
       </c>
       <c r="I16" s="11" t="str">
-        <f ca="1">IF(B16="","",IF(AND(D16&lt;&gt;"",TODAY()&lt;D16),"Programada",IF(AND(E16&lt;&gt;"",TODAY()&gt;E16),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vencida</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="23" customHeight="1">
       <c r="A17" s="5">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>34</v>
@@ -3613,7 +3619,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E17" s="10">
-        <v>46271.708333333336</v>
+        <v>46280.708333333336</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>35</v>
@@ -3625,16 +3631,16 @@
         <v>36</v>
       </c>
       <c r="I17" s="11" t="str">
-        <f ca="1">IF(B17="","",IF(AND(D17&lt;&gt;"",TODAY()&lt;D17),"Programada",IF(AND(E17&lt;&gt;"",TODAY()&gt;E17),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vencida</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="23" customHeight="1">
       <c r="A18" s="5">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>34</v>
@@ -3643,7 +3649,7 @@
         <v>46262.708333333336</v>
       </c>
       <c r="E18" s="10">
-        <v>46265.708333333336</v>
+        <v>46271.708333333336</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>35</v>
@@ -3655,25 +3661,25 @@
         <v>36</v>
       </c>
       <c r="I18" s="11" t="str">
-        <f ca="1">IF(B18="","",IF(AND(D18&lt;&gt;"",TODAY()&lt;D18),"Programada",IF(AND(E18&lt;&gt;"",TODAY()&gt;E18),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vencida</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="23" customHeight="1">
       <c r="A19" s="5">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="10">
-        <v>46278.708333333336</v>
+        <v>46262.708333333336</v>
       </c>
       <c r="E19" s="10">
-        <v>46280.708333333336</v>
+        <v>46265.708333333336</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>35</v>
@@ -3685,25 +3691,25 @@
         <v>36</v>
       </c>
       <c r="I19" s="11" t="str">
-        <f ca="1">IF(B19="","",IF(AND(D19&lt;&gt;"",TODAY()&lt;D19),"Programada",IF(AND(E19&lt;&gt;"",TODAY()&gt;E19),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vencida</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="23" customHeight="1">
       <c r="A20" s="5">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D20" s="10">
-        <v>46283.708333333336</v>
+        <v>46278.708333333336</v>
       </c>
       <c r="E20" s="10">
-        <v>46285.708333333336</v>
+        <v>46280.708333333336</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>35</v>
@@ -3715,16 +3721,16 @@
         <v>36</v>
       </c>
       <c r="I20" s="11" t="str">
-        <f ca="1">IF(B20="","",IF(AND(D20&lt;&gt;"",TODAY()&lt;D20),"Programada",IF(AND(E20&lt;&gt;"",TODAY()&gt;E20),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Vencida</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="23" customHeight="1">
       <c r="A21" s="5">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>11</v>
@@ -3733,7 +3739,7 @@
         <v>46283.708333333336</v>
       </c>
       <c r="E21" s="10">
-        <v>46292.708333333336</v>
+        <v>46285.708333333336</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>35</v>
@@ -3742,25 +3748,41 @@
         <v>35</v>
       </c>
       <c r="H21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="11" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Vencida</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="23" customHeight="1">
+      <c r="A22" s="5">
+        <v>96</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="10">
+        <v>46283.708333333336</v>
+      </c>
+      <c r="E22" s="10">
+        <v>46292.708333333336</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I21" s="11" t="str">
-        <f ca="1">IF(B21="","",IF(AND(D21&lt;&gt;"",TODAY()&lt;D21),"Programada",IF(AND(E21&lt;&gt;"",TODAY()&gt;E21),"Vencida","Vigente")))</f>
+      <c r="I22" s="11" t="str">
+        <f t="shared" ca="1" si="0"/>
         <v>Vigente</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="23" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="12" t="str">
-        <f ca="1">IF(B22="","",IF(AND(D22&lt;&gt;"",TODAY()&lt;D22),"Programada",IF(AND(E22&lt;&gt;"",TODAY()&gt;E22),"Vencida","Vigente")))</f>
-        <v/>
       </c>
     </row>
     <row r="23" spans="1:9" ht="23" customHeight="1">
@@ -3773,7 +3795,7 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="12" t="str">
-        <f ca="1">IF(B23="","",IF(AND(D23&lt;&gt;"",TODAY()&lt;D23),"Programada",IF(AND(E23&lt;&gt;"",TODAY()&gt;E23),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3787,7 +3809,7 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="12" t="str">
-        <f ca="1">IF(B24="","",IF(AND(D24&lt;&gt;"",TODAY()&lt;D24),"Programada",IF(AND(E24&lt;&gt;"",TODAY()&gt;E24),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3801,7 +3823,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="12" t="str">
-        <f ca="1">IF(B25="","",IF(AND(D25&lt;&gt;"",TODAY()&lt;D25),"Programada",IF(AND(E25&lt;&gt;"",TODAY()&gt;E25),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3815,7 +3837,7 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="12" t="str">
-        <f ca="1">IF(B26="","",IF(AND(D26&lt;&gt;"",TODAY()&lt;D26),"Programada",IF(AND(E26&lt;&gt;"",TODAY()&gt;E26),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3829,7 +3851,7 @@
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="12" t="str">
-        <f ca="1">IF(B27="","",IF(AND(D27&lt;&gt;"",TODAY()&lt;D27),"Programada",IF(AND(E27&lt;&gt;"",TODAY()&gt;E27),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3843,7 +3865,7 @@
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="12" t="str">
-        <f ca="1">IF(B28="","",IF(AND(D28&lt;&gt;"",TODAY()&lt;D28),"Programada",IF(AND(E28&lt;&gt;"",TODAY()&gt;E28),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3857,7 +3879,7 @@
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="12" t="str">
-        <f ca="1">IF(B29="","",IF(AND(D29&lt;&gt;"",TODAY()&lt;D29),"Programada",IF(AND(E29&lt;&gt;"",TODAY()&gt;E29),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3871,7 +3893,7 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="12" t="str">
-        <f ca="1">IF(B30="","",IF(AND(D30&lt;&gt;"",TODAY()&lt;D30),"Programada",IF(AND(E30&lt;&gt;"",TODAY()&gt;E30),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3885,7 +3907,7 @@
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="12" t="str">
-        <f ca="1">IF(B31="","",IF(AND(D31&lt;&gt;"",TODAY()&lt;D31),"Programada",IF(AND(E31&lt;&gt;"",TODAY()&gt;E31),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3899,7 +3921,7 @@
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="12" t="str">
-        <f ca="1">IF(B32="","",IF(AND(D32&lt;&gt;"",TODAY()&lt;D32),"Programada",IF(AND(E32&lt;&gt;"",TODAY()&gt;E32),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3913,7 +3935,7 @@
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="12" t="str">
-        <f ca="1">IF(B33="","",IF(AND(D33&lt;&gt;"",TODAY()&lt;D33),"Programada",IF(AND(E33&lt;&gt;"",TODAY()&gt;E33),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3927,7 +3949,7 @@
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="12" t="str">
-        <f ca="1">IF(B34="","",IF(AND(D34&lt;&gt;"",TODAY()&lt;D34),"Programada",IF(AND(E34&lt;&gt;"",TODAY()&gt;E34),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3941,7 +3963,7 @@
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="12" t="str">
-        <f ca="1">IF(B35="","",IF(AND(D35&lt;&gt;"",TODAY()&lt;D35),"Programada",IF(AND(E35&lt;&gt;"",TODAY()&gt;E35),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3955,7 +3977,7 @@
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="12" t="str">
-        <f ca="1">IF(B36="","",IF(AND(D36&lt;&gt;"",TODAY()&lt;D36),"Programada",IF(AND(E36&lt;&gt;"",TODAY()&gt;E36),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3969,7 +3991,7 @@
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="12" t="str">
-        <f ca="1">IF(B37="","",IF(AND(D37&lt;&gt;"",TODAY()&lt;D37),"Programada",IF(AND(E37&lt;&gt;"",TODAY()&gt;E37),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3983,7 +4005,7 @@
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="12" t="str">
-        <f ca="1">IF(B38="","",IF(AND(D38&lt;&gt;"",TODAY()&lt;D38),"Programada",IF(AND(E38&lt;&gt;"",TODAY()&gt;E38),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -3997,7 +4019,7 @@
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="12" t="str">
-        <f ca="1">IF(B39="","",IF(AND(D39&lt;&gt;"",TODAY()&lt;D39),"Programada",IF(AND(E39&lt;&gt;"",TODAY()&gt;E39),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -4011,7 +4033,7 @@
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="12" t="str">
-        <f ca="1">IF(B40="","",IF(AND(D40&lt;&gt;"",TODAY()&lt;D40),"Programada",IF(AND(E40&lt;&gt;"",TODAY()&gt;E40),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -4025,23 +4047,37 @@
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="12" t="str">
-        <f ca="1">IF(B41="","",IF(AND(D41&lt;&gt;"",TODAY()&lt;D41),"Programada",IF(AND(E41&lt;&gt;"",TODAY()&gt;E41),"Vencida","Vigente")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
+    <row r="42" spans="1:9" ht="23" customHeight="1">
+      <c r="A42" s="9"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="12" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:I41">
-    <sortCondition ref="A4:A41"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:I42">
+    <sortCondition ref="A4:A42"/>
   </sortState>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:G41" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="F5:G42" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Si,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H5:H41" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="H5:H42" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2F6088-ED10-4CF5-A6B8-42B140F6D6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B52CD66-7C47-44AD-990B-EBF9D7003488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>
@@ -132,9 +132,6 @@
     <t>Registra y evidencia jarras completas, sin daños y listas para operar.</t>
   </si>
   <si>
-    <t>Organizacion Refrigeradores Back</t>
-  </si>
-  <si>
     <t>Valida el acomodo de refrigeradores de Back y optimiza espacios</t>
   </si>
   <si>
@@ -2776,6 +2773,9 @@
   </si>
   <si>
     <t>Valida Insumos  FHW Cubiertos &amp; Taza 3 Oz</t>
+  </si>
+  <si>
+    <t>Organización Refrigeradores Back</t>
   </si>
 </sst>
 </file>
@@ -3173,8 +3173,8 @@
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="58" customWidth="1"/>
     <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14.25" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="2" spans="1:9" ht="28" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -3262,10 +3262,10 @@
         <v>46300.708333333336</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>17</v>
@@ -3343,7 +3343,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D8" s="10">
         <v>46283.708333333336</v>
@@ -3490,10 +3490,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="D13" s="10">
         <v>46283.708333333336</v>
@@ -3520,10 +3520,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>909</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>910</v>
       </c>
       <c r="D14" s="10">
         <v>46283.708333333336</v>
@@ -3535,7 +3535,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>13</v>
@@ -3550,10 +3550,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>910</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>911</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>912</v>
       </c>
       <c r="D15" s="10">
         <v>46283.708333333336</v>
@@ -3580,10 +3580,10 @@
         <v>90</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="D16" s="10">
         <v>46262.708333333336</v>
@@ -3592,13 +3592,13 @@
         <v>46268.708333333336</v>
       </c>
       <c r="F16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="I16" s="11" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3610,10 +3610,10 @@
         <v>91</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="10">
         <v>46262.708333333336</v>
@@ -3622,13 +3622,13 @@
         <v>46280.708333333336</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="I17" s="11" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3640,10 +3640,10 @@
         <v>92</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" s="10">
         <v>46262.708333333336</v>
@@ -3652,13 +3652,13 @@
         <v>46271.708333333336</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="I18" s="11" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3670,10 +3670,10 @@
         <v>93</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" s="10">
         <v>46262.708333333336</v>
@@ -3682,13 +3682,13 @@
         <v>46265.708333333336</v>
       </c>
       <c r="F19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="I19" s="11" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3700,10 +3700,10 @@
         <v>94</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" s="10">
         <v>46278.708333333336</v>
@@ -3712,13 +3712,13 @@
         <v>46280.708333333336</v>
       </c>
       <c r="F20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="I20" s="11" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3742,13 +3742,13 @@
         <v>46285.708333333336</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="I21" s="11" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3772,10 +3772,10 @@
         <v>46292.708333333336</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>13</v>
@@ -4100,7 +4100,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="2" spans="1:6" ht="32" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>6</v>
@@ -4148,17 +4148,17 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>61</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>62</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>12</v>
@@ -4166,17 +4166,17 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>64</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>65</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>12</v>
@@ -4184,17 +4184,17 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>12</v>
@@ -4202,17 +4202,17 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>69</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>12</v>
@@ -4220,17 +4220,17 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>70</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>71</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>12</v>
@@ -4238,17 +4238,17 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>12</v>
@@ -4256,19 +4256,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="E11" s="14" t="s">
         <v>76</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>77</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>12</v>
@@ -4276,19 +4276,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="D12" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>80</v>
-      </c>
       <c r="E12" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>12</v>
@@ -4296,19 +4296,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>83</v>
-      </c>
       <c r="E13" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>12</v>
@@ -4316,19 +4316,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="14" t="s">
+      <c r="D14" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>86</v>
-      </c>
       <c r="E14" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>12</v>
@@ -4336,19 +4336,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="D15" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>89</v>
-      </c>
       <c r="E15" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F15" s="14" t="s">
         <v>12</v>
@@ -4356,19 +4356,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="D16" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>92</v>
-      </c>
       <c r="E16" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>12</v>
@@ -4376,19 +4376,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="C17" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="D17" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>96</v>
-      </c>
       <c r="E17" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>12</v>
@@ -4396,19 +4396,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="D18" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>99</v>
-      </c>
       <c r="E18" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>12</v>
@@ -4416,19 +4416,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="14" t="s">
+      <c r="D19" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>102</v>
-      </c>
       <c r="E19" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>12</v>
@@ -4436,19 +4436,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="14" t="s">
+      <c r="D20" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>105</v>
-      </c>
       <c r="E20" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>12</v>
@@ -4456,19 +4456,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="14" t="s">
+      <c r="D21" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>108</v>
-      </c>
       <c r="E21" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>12</v>
@@ -4476,19 +4476,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="14" t="s">
+      <c r="D22" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>111</v>
-      </c>
       <c r="E22" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>12</v>
@@ -4496,19 +4496,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="14" t="s">
+      <c r="D23" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>114</v>
-      </c>
       <c r="E23" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>12</v>
@@ -4516,19 +4516,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="14" t="s">
+      <c r="D24" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D24" s="14" t="s">
-        <v>117</v>
-      </c>
       <c r="E24" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>12</v>
@@ -4536,19 +4536,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="C25" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="D25" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>121</v>
-      </c>
       <c r="E25" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>12</v>
@@ -4556,19 +4556,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="14" t="s">
+      <c r="D26" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="14" t="s">
-        <v>124</v>
-      </c>
       <c r="E26" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>12</v>
@@ -4576,19 +4576,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B27" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27" s="14" t="s">
+      <c r="D27" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="14" t="s">
-        <v>127</v>
-      </c>
       <c r="E27" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>12</v>
@@ -4596,19 +4596,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" s="14" t="s">
+      <c r="D28" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="14" t="s">
-        <v>130</v>
-      </c>
       <c r="E28" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>12</v>
@@ -4616,19 +4616,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" s="14" t="s">
+      <c r="D29" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="14" t="s">
-        <v>133</v>
-      </c>
       <c r="E29" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>12</v>
@@ -4636,19 +4636,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="14" t="s">
+      <c r="D30" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>136</v>
-      </c>
       <c r="E30" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>12</v>
@@ -4656,19 +4656,19 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C31" s="14" t="s">
+      <c r="D31" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="14" t="s">
-        <v>139</v>
-      </c>
       <c r="E31" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>12</v>
@@ -4676,19 +4676,19 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="14" t="s">
+      <c r="D32" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="14" t="s">
-        <v>142</v>
-      </c>
       <c r="E32" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>12</v>
@@ -4727,7 +4727,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="28" customHeight="1">
       <c r="A1" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="2" spans="1:7" ht="32" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -4758,19 +4758,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>6</v>
@@ -4784,16 +4784,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>146</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>147</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>12</v>
@@ -4807,16 +4807,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>150</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>12</v>
@@ -4830,16 +4830,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>151</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>152</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>12</v>
@@ -4853,16 +4853,16 @@
         <v>2</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>153</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>154</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>12</v>
@@ -4876,16 +4876,16 @@
         <v>2</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>155</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>156</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>12</v>
@@ -4922,7 +4922,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4931,7 +4931,7 @@
     </row>
     <row r="2" spans="1:5" ht="32" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -4947,6088 +4947,6088 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>159</v>
-      </c>
       <c r="C5" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>162</v>
-      </c>
       <c r="C6" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>164</v>
-      </c>
       <c r="C7" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>166</v>
-      </c>
       <c r="C8" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>168</v>
-      </c>
       <c r="C9" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>170</v>
-      </c>
       <c r="C10" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>172</v>
-      </c>
       <c r="C11" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>174</v>
-      </c>
       <c r="C12" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>176</v>
-      </c>
       <c r="C13" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>178</v>
-      </c>
       <c r="C14" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>180</v>
-      </c>
       <c r="C15" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>182</v>
-      </c>
       <c r="C16" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="15" t="s">
-        <v>184</v>
-      </c>
       <c r="C17" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>186</v>
-      </c>
       <c r="C18" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B19" s="15" t="s">
-        <v>188</v>
-      </c>
       <c r="C19" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>190</v>
-      </c>
       <c r="C20" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>192</v>
-      </c>
       <c r="C21" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>194</v>
-      </c>
       <c r="C22" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>196</v>
-      </c>
       <c r="C23" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>198</v>
-      </c>
       <c r="C24" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>200</v>
-      </c>
       <c r="C25" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>202</v>
-      </c>
       <c r="C26" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="B27" s="15" t="s">
-        <v>204</v>
-      </c>
       <c r="C27" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="B28" s="15" t="s">
-        <v>206</v>
-      </c>
       <c r="C28" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>208</v>
-      </c>
       <c r="C29" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>210</v>
-      </c>
       <c r="C30" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>212</v>
-      </c>
       <c r="C31" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B32" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>214</v>
-      </c>
       <c r="C32" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>216</v>
-      </c>
       <c r="C33" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>218</v>
-      </c>
       <c r="C34" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>220</v>
-      </c>
       <c r="C35" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>222</v>
-      </c>
       <c r="C36" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B37" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>224</v>
-      </c>
       <c r="C37" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B38" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>226</v>
-      </c>
       <c r="C38" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>228</v>
-      </c>
       <c r="C39" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>230</v>
-      </c>
       <c r="C40" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B41" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>232</v>
-      </c>
       <c r="C41" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B42" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="B42" s="15" t="s">
-        <v>234</v>
-      </c>
       <c r="C42" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B43" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>236</v>
-      </c>
       <c r="C43" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B44" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>238</v>
-      </c>
       <c r="C44" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B45" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>240</v>
-      </c>
       <c r="C45" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="B46" s="15" t="s">
-        <v>242</v>
-      </c>
       <c r="C46" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="B47" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>244</v>
-      </c>
       <c r="C47" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B48" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="B48" s="15" t="s">
-        <v>246</v>
-      </c>
       <c r="C48" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B49" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="B49" s="15" t="s">
-        <v>248</v>
-      </c>
       <c r="C49" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B50" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="B50" s="15" t="s">
-        <v>250</v>
-      </c>
       <c r="C50" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="B51" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="B51" s="15" t="s">
-        <v>252</v>
-      </c>
       <c r="C51" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B52" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="B52" s="15" t="s">
-        <v>254</v>
-      </c>
       <c r="C52" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B53" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="B53" s="15" t="s">
-        <v>256</v>
-      </c>
       <c r="C53" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B54" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="B54" s="15" t="s">
-        <v>258</v>
-      </c>
       <c r="C54" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B55" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="B55" s="15" t="s">
-        <v>260</v>
-      </c>
       <c r="C55" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B56" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="B56" s="15" t="s">
-        <v>262</v>
-      </c>
       <c r="C56" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="B57" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="B57" s="15" t="s">
-        <v>264</v>
-      </c>
       <c r="C57" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B58" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="B58" s="15" t="s">
-        <v>266</v>
-      </c>
       <c r="C58" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B59" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="B59" s="15" t="s">
-        <v>268</v>
-      </c>
       <c r="C59" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="B60" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="B60" s="15" t="s">
-        <v>270</v>
-      </c>
       <c r="C60" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B61" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B61" s="15" t="s">
-        <v>272</v>
-      </c>
       <c r="C61" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B62" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="B62" s="15" t="s">
-        <v>274</v>
-      </c>
       <c r="C62" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B63" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="B63" s="15" t="s">
-        <v>276</v>
-      </c>
       <c r="C63" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B64" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="B64" s="15" t="s">
-        <v>278</v>
-      </c>
       <c r="C64" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="B65" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="B65" s="15" t="s">
-        <v>280</v>
-      </c>
       <c r="C65" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B66" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="B66" s="15" t="s">
-        <v>282</v>
-      </c>
       <c r="C66" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B67" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="B67" s="15" t="s">
-        <v>284</v>
-      </c>
       <c r="C67" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="B68" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="B68" s="15" t="s">
-        <v>286</v>
-      </c>
       <c r="C68" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="B69" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="B69" s="15" t="s">
-        <v>288</v>
-      </c>
       <c r="C69" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="B70" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="B70" s="15" t="s">
-        <v>290</v>
-      </c>
       <c r="C70" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B71" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="B71" s="15" t="s">
-        <v>292</v>
-      </c>
       <c r="C71" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="B72" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="B72" s="15" t="s">
-        <v>294</v>
-      </c>
       <c r="C72" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B73" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B73" s="15" t="s">
-        <v>296</v>
-      </c>
       <c r="C73" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B74" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="B74" s="15" t="s">
-        <v>298</v>
-      </c>
       <c r="C74" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="B75" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="B75" s="15" t="s">
-        <v>300</v>
-      </c>
       <c r="C75" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="B76" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="B76" s="15" t="s">
-        <v>302</v>
-      </c>
       <c r="C76" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="B77" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="B77" s="15" t="s">
-        <v>304</v>
-      </c>
       <c r="C77" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="B78" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="B78" s="15" t="s">
-        <v>306</v>
-      </c>
       <c r="C78" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="B79" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="B79" s="15" t="s">
-        <v>308</v>
-      </c>
       <c r="C79" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="B80" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="B80" s="15" t="s">
-        <v>310</v>
-      </c>
       <c r="C80" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B81" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="B81" s="15" t="s">
-        <v>312</v>
-      </c>
       <c r="C81" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="B82" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="B82" s="15" t="s">
-        <v>314</v>
-      </c>
       <c r="C82" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="B83" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="B83" s="15" t="s">
-        <v>316</v>
-      </c>
       <c r="C83" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B84" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="B84" s="15" t="s">
-        <v>318</v>
-      </c>
       <c r="C84" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B85" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="B85" s="15" t="s">
-        <v>320</v>
-      </c>
       <c r="C85" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="B86" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="B86" s="15" t="s">
-        <v>322</v>
-      </c>
       <c r="C86" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="B87" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="B87" s="15" t="s">
-        <v>324</v>
-      </c>
       <c r="C87" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="B88" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="B88" s="15" t="s">
-        <v>326</v>
-      </c>
       <c r="C88" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B89" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="B89" s="15" t="s">
-        <v>328</v>
-      </c>
       <c r="C89" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="B90" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B90" s="15" t="s">
-        <v>330</v>
-      </c>
       <c r="C90" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B91" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="B91" s="15" t="s">
-        <v>332</v>
-      </c>
       <c r="C91" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="B92" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="B92" s="15" t="s">
-        <v>334</v>
-      </c>
       <c r="C92" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="B93" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="B93" s="15" t="s">
-        <v>336</v>
-      </c>
       <c r="C93" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="B94" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="B94" s="15" t="s">
-        <v>338</v>
-      </c>
       <c r="C94" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="B95" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="B95" s="15" t="s">
-        <v>340</v>
-      </c>
       <c r="C95" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="B96" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B96" s="15" t="s">
-        <v>342</v>
-      </c>
       <c r="C96" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="B97" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="B97" s="15" t="s">
-        <v>344</v>
-      </c>
       <c r="C97" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B98" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="B98" s="15" t="s">
-        <v>346</v>
-      </c>
       <c r="C98" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="B99" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="B99" s="15" t="s">
-        <v>348</v>
-      </c>
       <c r="C99" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="B100" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="B100" s="15" t="s">
-        <v>350</v>
-      </c>
       <c r="C100" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="B101" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="B101" s="15" t="s">
-        <v>352</v>
-      </c>
       <c r="C101" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="B102" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="B102" s="15" t="s">
-        <v>354</v>
-      </c>
       <c r="C102" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="B103" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="B103" s="15" t="s">
-        <v>356</v>
-      </c>
       <c r="C103" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B104" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="B104" s="15" t="s">
-        <v>358</v>
-      </c>
       <c r="C104" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="B105" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="B105" s="15" t="s">
-        <v>360</v>
-      </c>
       <c r="C105" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="B106" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="B106" s="15" t="s">
-        <v>362</v>
-      </c>
       <c r="C106" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="B107" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="B107" s="15" t="s">
-        <v>364</v>
-      </c>
       <c r="C107" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="B108" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="B108" s="15" t="s">
-        <v>366</v>
-      </c>
       <c r="C108" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="B109" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="B109" s="15" t="s">
-        <v>368</v>
-      </c>
       <c r="C109" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="B110" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="B110" s="15" t="s">
-        <v>370</v>
-      </c>
       <c r="C110" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="B111" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="B111" s="15" t="s">
-        <v>372</v>
-      </c>
       <c r="C111" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="B112" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="B112" s="15" t="s">
-        <v>374</v>
-      </c>
       <c r="C112" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="B113" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="B113" s="15" t="s">
-        <v>376</v>
-      </c>
       <c r="C113" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="B114" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="B114" s="15" t="s">
-        <v>378</v>
-      </c>
       <c r="C114" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="B115" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="B115" s="15" t="s">
-        <v>380</v>
-      </c>
       <c r="C115" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="B116" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="B116" s="15" t="s">
-        <v>382</v>
-      </c>
       <c r="C116" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="B117" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="B117" s="15" t="s">
-        <v>384</v>
-      </c>
       <c r="C117" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="B118" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="B118" s="15" t="s">
-        <v>386</v>
-      </c>
       <c r="C118" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="B119" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="B119" s="15" t="s">
-        <v>388</v>
-      </c>
       <c r="C119" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="B120" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="B120" s="15" t="s">
-        <v>390</v>
-      </c>
       <c r="C120" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="B121" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="B121" s="15" t="s">
-        <v>392</v>
-      </c>
       <c r="C121" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="B122" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="B122" s="15" t="s">
-        <v>394</v>
-      </c>
       <c r="C122" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="B123" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="B123" s="15" t="s">
-        <v>396</v>
-      </c>
       <c r="C123" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="B124" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="B124" s="15" t="s">
-        <v>398</v>
-      </c>
       <c r="C124" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="B125" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="B125" s="15" t="s">
-        <v>400</v>
-      </c>
       <c r="C125" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="B126" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="B126" s="15" t="s">
-        <v>402</v>
-      </c>
       <c r="C126" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="B127" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="B127" s="15" t="s">
-        <v>404</v>
-      </c>
       <c r="C127" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="B128" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="B128" s="15" t="s">
-        <v>406</v>
-      </c>
       <c r="C128" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="B129" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="B129" s="15" t="s">
-        <v>408</v>
-      </c>
       <c r="C129" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="B130" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="B130" s="15" t="s">
-        <v>410</v>
-      </c>
       <c r="C130" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="B131" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="B131" s="15" t="s">
-        <v>412</v>
-      </c>
       <c r="C131" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="B132" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="B132" s="15" t="s">
-        <v>414</v>
-      </c>
       <c r="C132" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="B133" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="B133" s="15" t="s">
-        <v>416</v>
-      </c>
       <c r="C133" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="B134" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="B134" s="15" t="s">
-        <v>418</v>
-      </c>
       <c r="C134" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="B135" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="B135" s="15" t="s">
-        <v>420</v>
-      </c>
       <c r="C135" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="B136" s="15" t="s">
         <v>421</v>
       </c>
-      <c r="B136" s="15" t="s">
-        <v>422</v>
-      </c>
       <c r="C136" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="B137" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="B137" s="15" t="s">
-        <v>424</v>
-      </c>
       <c r="C137" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="B138" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="B138" s="15" t="s">
-        <v>426</v>
-      </c>
       <c r="C138" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D138" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="B139" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="B139" s="15" t="s">
-        <v>428</v>
-      </c>
       <c r="C139" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="B140" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="B140" s="15" t="s">
-        <v>430</v>
-      </c>
       <c r="C140" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E140" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B141" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="B141" s="15" t="s">
-        <v>432</v>
-      </c>
       <c r="C141" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D141" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="B142" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="B142" s="15" t="s">
-        <v>434</v>
-      </c>
       <c r="C142" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="B143" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="B143" s="15" t="s">
-        <v>436</v>
-      </c>
       <c r="C143" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D143" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="B144" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="B144" s="15" t="s">
-        <v>438</v>
-      </c>
       <c r="C144" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="B145" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="15" t="s">
-        <v>440</v>
-      </c>
       <c r="C145" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D145" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="B146" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="B146" s="15" t="s">
-        <v>442</v>
-      </c>
       <c r="C146" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="B147" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="B147" s="15" t="s">
-        <v>444</v>
-      </c>
       <c r="C147" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="B148" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="B148" s="15" t="s">
-        <v>446</v>
-      </c>
       <c r="C148" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D148" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="B149" s="15" t="s">
         <v>447</v>
       </c>
-      <c r="B149" s="15" t="s">
-        <v>448</v>
-      </c>
       <c r="C149" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D149" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="B150" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="B150" s="15" t="s">
-        <v>450</v>
-      </c>
       <c r="C150" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="B151" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="B151" s="15" t="s">
-        <v>452</v>
-      </c>
       <c r="C151" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="B152" s="15" t="s">
         <v>453</v>
       </c>
-      <c r="B152" s="15" t="s">
-        <v>454</v>
-      </c>
       <c r="C152" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="B153" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="B153" s="15" t="s">
-        <v>456</v>
-      </c>
       <c r="C153" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="B154" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="B154" s="15" t="s">
-        <v>458</v>
-      </c>
       <c r="C154" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E154" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="B155" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="B155" s="15" t="s">
-        <v>460</v>
-      </c>
       <c r="C155" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D155" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="B156" s="15" t="s">
         <v>461</v>
       </c>
-      <c r="B156" s="15" t="s">
-        <v>462</v>
-      </c>
       <c r="C156" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E156" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="B157" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="B157" s="15" t="s">
-        <v>464</v>
-      </c>
       <c r="C157" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E157" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="B158" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="B158" s="15" t="s">
-        <v>466</v>
-      </c>
       <c r="C158" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="B159" s="15" t="s">
         <v>467</v>
       </c>
-      <c r="B159" s="15" t="s">
-        <v>468</v>
-      </c>
       <c r="C159" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E159" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="B160" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="B160" s="15" t="s">
-        <v>470</v>
-      </c>
       <c r="C160" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="B161" s="15" t="s">
         <v>471</v>
       </c>
-      <c r="B161" s="15" t="s">
-        <v>472</v>
-      </c>
       <c r="C161" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="B162" s="15" t="s">
         <v>473</v>
       </c>
-      <c r="B162" s="15" t="s">
-        <v>474</v>
-      </c>
       <c r="C162" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E162" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="B163" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="B163" s="15" t="s">
-        <v>476</v>
-      </c>
       <c r="C163" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E163" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="B164" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="B164" s="15" t="s">
-        <v>478</v>
-      </c>
       <c r="C164" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E164" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="B165" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="B165" s="15" t="s">
-        <v>480</v>
-      </c>
       <c r="C165" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E165" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="B166" s="15" t="s">
         <v>481</v>
       </c>
-      <c r="B166" s="15" t="s">
-        <v>482</v>
-      </c>
       <c r="C166" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="B167" s="15" t="s">
         <v>483</v>
       </c>
-      <c r="B167" s="15" t="s">
-        <v>484</v>
-      </c>
       <c r="C167" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E167" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="B168" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="B168" s="15" t="s">
-        <v>486</v>
-      </c>
       <c r="C168" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E168" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="B169" s="15" t="s">
         <v>487</v>
       </c>
-      <c r="B169" s="15" t="s">
-        <v>488</v>
-      </c>
       <c r="C169" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E169" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="B170" s="15" t="s">
         <v>489</v>
       </c>
-      <c r="B170" s="15" t="s">
-        <v>490</v>
-      </c>
       <c r="C170" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E170" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="B171" s="15" t="s">
         <v>491</v>
       </c>
-      <c r="B171" s="15" t="s">
-        <v>492</v>
-      </c>
       <c r="C171" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E171" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="B172" s="15" t="s">
         <v>493</v>
       </c>
-      <c r="B172" s="15" t="s">
-        <v>494</v>
-      </c>
       <c r="C172" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E172" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="B173" s="15" t="s">
         <v>495</v>
       </c>
-      <c r="B173" s="15" t="s">
-        <v>496</v>
-      </c>
       <c r="C173" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E173" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="B174" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="B174" s="15" t="s">
-        <v>498</v>
-      </c>
       <c r="C174" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E174" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="B175" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="B175" s="15" t="s">
-        <v>500</v>
-      </c>
       <c r="C175" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E175" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="B176" s="15" t="s">
         <v>501</v>
       </c>
-      <c r="B176" s="15" t="s">
-        <v>502</v>
-      </c>
       <c r="C176" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E176" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="B177" s="15" t="s">
         <v>503</v>
       </c>
-      <c r="B177" s="15" t="s">
-        <v>504</v>
-      </c>
       <c r="C177" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E177" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="B178" s="15" t="s">
         <v>505</v>
       </c>
-      <c r="B178" s="15" t="s">
-        <v>506</v>
-      </c>
       <c r="C178" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E178" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="B179" s="15" t="s">
         <v>507</v>
       </c>
-      <c r="B179" s="15" t="s">
-        <v>508</v>
-      </c>
       <c r="C179" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E179" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="B180" s="15" t="s">
         <v>509</v>
       </c>
-      <c r="B180" s="15" t="s">
-        <v>510</v>
-      </c>
       <c r="C180" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E180" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="B181" s="15" t="s">
         <v>511</v>
       </c>
-      <c r="B181" s="15" t="s">
-        <v>512</v>
-      </c>
       <c r="C181" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D181" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E181" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="B182" s="15" t="s">
         <v>513</v>
       </c>
-      <c r="B182" s="15" t="s">
-        <v>514</v>
-      </c>
       <c r="C182" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D182" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E182" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="B183" s="15" t="s">
         <v>515</v>
       </c>
-      <c r="B183" s="15" t="s">
-        <v>516</v>
-      </c>
       <c r="C183" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D183" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E183" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="B184" s="15" t="s">
         <v>517</v>
       </c>
-      <c r="B184" s="15" t="s">
-        <v>518</v>
-      </c>
       <c r="C184" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E184" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="B185" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="B185" s="15" t="s">
-        <v>520</v>
-      </c>
       <c r="C185" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D185" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E185" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="B186" s="15" t="s">
         <v>521</v>
       </c>
-      <c r="B186" s="15" t="s">
-        <v>522</v>
-      </c>
       <c r="C186" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D186" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E186" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="B187" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="B187" s="15" t="s">
-        <v>524</v>
-      </c>
       <c r="C187" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D187" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E187" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="B188" s="15" t="s">
         <v>525</v>
       </c>
-      <c r="B188" s="15" t="s">
-        <v>526</v>
-      </c>
       <c r="C188" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D188" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E188" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="B189" s="15" t="s">
         <v>527</v>
       </c>
-      <c r="B189" s="15" t="s">
-        <v>528</v>
-      </c>
       <c r="C189" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E189" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="B190" s="15" t="s">
         <v>529</v>
       </c>
-      <c r="B190" s="15" t="s">
-        <v>530</v>
-      </c>
       <c r="C190" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E190" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="15" t="s">
+        <v>530</v>
+      </c>
+      <c r="B191" s="15" t="s">
         <v>531</v>
       </c>
-      <c r="B191" s="15" t="s">
-        <v>532</v>
-      </c>
       <c r="C191" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E191" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="B192" s="15" t="s">
         <v>533</v>
       </c>
-      <c r="B192" s="15" t="s">
-        <v>534</v>
-      </c>
       <c r="C192" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E192" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="B193" s="15" t="s">
         <v>535</v>
       </c>
-      <c r="B193" s="15" t="s">
-        <v>536</v>
-      </c>
       <c r="C193" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D193" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E193" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="B194" s="15" t="s">
         <v>537</v>
       </c>
-      <c r="B194" s="15" t="s">
-        <v>538</v>
-      </c>
       <c r="C194" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D194" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E194" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="B195" s="15" t="s">
         <v>539</v>
       </c>
-      <c r="B195" s="15" t="s">
-        <v>540</v>
-      </c>
       <c r="C195" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D195" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E195" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="B196" s="15" t="s">
         <v>541</v>
       </c>
-      <c r="B196" s="15" t="s">
-        <v>542</v>
-      </c>
       <c r="C196" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E196" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="B197" s="15" t="s">
         <v>543</v>
       </c>
-      <c r="B197" s="15" t="s">
-        <v>544</v>
-      </c>
       <c r="C197" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E197" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="B198" s="15" t="s">
         <v>545</v>
       </c>
-      <c r="B198" s="15" t="s">
-        <v>546</v>
-      </c>
       <c r="C198" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E198" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="B199" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="B199" s="15" t="s">
-        <v>548</v>
-      </c>
       <c r="C199" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E199" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="B200" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="B200" s="15" t="s">
-        <v>550</v>
-      </c>
       <c r="C200" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E200" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="B201" s="15" t="s">
         <v>551</v>
       </c>
-      <c r="B201" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="C201" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E201" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="B202" s="15" t="s">
         <v>553</v>
       </c>
-      <c r="B202" s="15" t="s">
-        <v>554</v>
-      </c>
       <c r="C202" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E202" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="B203" s="15" t="s">
         <v>555</v>
       </c>
-      <c r="B203" s="15" t="s">
-        <v>556</v>
-      </c>
       <c r="C203" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E203" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="B204" s="15" t="s">
         <v>557</v>
       </c>
-      <c r="B204" s="15" t="s">
-        <v>558</v>
-      </c>
       <c r="C204" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E204" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="B205" s="15" t="s">
         <v>559</v>
       </c>
-      <c r="B205" s="15" t="s">
-        <v>560</v>
-      </c>
       <c r="C205" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D205" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E205" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="B206" s="15" t="s">
         <v>561</v>
       </c>
-      <c r="B206" s="15" t="s">
-        <v>562</v>
-      </c>
       <c r="C206" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E206" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="B207" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="B207" s="15" t="s">
-        <v>564</v>
-      </c>
       <c r="C207" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E207" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="B208" s="15" t="s">
         <v>565</v>
       </c>
-      <c r="B208" s="15" t="s">
-        <v>566</v>
-      </c>
       <c r="C208" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E208" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="B209" s="15" t="s">
         <v>567</v>
       </c>
-      <c r="B209" s="15" t="s">
-        <v>568</v>
-      </c>
       <c r="C209" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E209" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="B210" s="15" t="s">
         <v>569</v>
       </c>
-      <c r="B210" s="15" t="s">
-        <v>570</v>
-      </c>
       <c r="C210" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E210" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="15" t="s">
+        <v>570</v>
+      </c>
+      <c r="B211" s="15" t="s">
         <v>571</v>
       </c>
-      <c r="B211" s="15" t="s">
-        <v>572</v>
-      </c>
       <c r="C211" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E211" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="B212" s="15" t="s">
         <v>573</v>
       </c>
-      <c r="B212" s="15" t="s">
-        <v>574</v>
-      </c>
       <c r="C212" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E212" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="B213" s="15" t="s">
         <v>575</v>
       </c>
-      <c r="B213" s="15" t="s">
-        <v>576</v>
-      </c>
       <c r="C213" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E213" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="B214" s="15" t="s">
         <v>577</v>
       </c>
-      <c r="B214" s="15" t="s">
-        <v>578</v>
-      </c>
       <c r="C214" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E214" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="B215" s="15" t="s">
         <v>579</v>
       </c>
-      <c r="B215" s="15" t="s">
-        <v>580</v>
-      </c>
       <c r="C215" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E215" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="B216" s="15" t="s">
         <v>581</v>
       </c>
-      <c r="B216" s="15" t="s">
-        <v>582</v>
-      </c>
       <c r="C216" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E216" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="B217" s="15" t="s">
         <v>583</v>
       </c>
-      <c r="B217" s="15" t="s">
-        <v>584</v>
-      </c>
       <c r="C217" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E217" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="15" t="s">
+        <v>584</v>
+      </c>
+      <c r="B218" s="15" t="s">
         <v>585</v>
       </c>
-      <c r="B218" s="15" t="s">
-        <v>586</v>
-      </c>
       <c r="C218" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E218" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="15" t="s">
+        <v>586</v>
+      </c>
+      <c r="B219" s="15" t="s">
         <v>587</v>
       </c>
-      <c r="B219" s="15" t="s">
-        <v>588</v>
-      </c>
       <c r="C219" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E219" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="15" t="s">
+        <v>588</v>
+      </c>
+      <c r="B220" s="15" t="s">
         <v>589</v>
       </c>
-      <c r="B220" s="15" t="s">
-        <v>590</v>
-      </c>
       <c r="C220" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D220" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E220" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="B221" s="15" t="s">
         <v>591</v>
       </c>
-      <c r="B221" s="15" t="s">
-        <v>592</v>
-      </c>
       <c r="C221" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E221" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="B222" s="15" t="s">
         <v>593</v>
       </c>
-      <c r="B222" s="15" t="s">
-        <v>594</v>
-      </c>
       <c r="C222" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E222" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="B223" s="15" t="s">
         <v>595</v>
       </c>
-      <c r="B223" s="15" t="s">
-        <v>596</v>
-      </c>
       <c r="C223" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D223" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E223" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="B224" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="B224" s="15" t="s">
-        <v>598</v>
-      </c>
       <c r="C224" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D224" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E224" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="B225" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="B225" s="15" t="s">
-        <v>600</v>
-      </c>
       <c r="C225" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D225" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E225" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="15" t="s">
+        <v>600</v>
+      </c>
+      <c r="B226" s="15" t="s">
         <v>601</v>
       </c>
-      <c r="B226" s="15" t="s">
-        <v>602</v>
-      </c>
       <c r="C226" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D226" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E226" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="B227" s="15" t="s">
         <v>603</v>
       </c>
-      <c r="B227" s="15" t="s">
-        <v>604</v>
-      </c>
       <c r="C227" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D227" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E227" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="15" t="s">
+        <v>604</v>
+      </c>
+      <c r="B228" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="B228" s="15" t="s">
-        <v>606</v>
-      </c>
       <c r="C228" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D228" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E228" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="B229" s="15" t="s">
         <v>607</v>
       </c>
-      <c r="B229" s="15" t="s">
-        <v>608</v>
-      </c>
       <c r="C229" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D229" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E229" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="B230" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="B230" s="15" t="s">
-        <v>610</v>
-      </c>
       <c r="C230" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D230" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E230" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="B231" s="15" t="s">
         <v>611</v>
       </c>
-      <c r="B231" s="15" t="s">
-        <v>612</v>
-      </c>
       <c r="C231" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D231" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E231" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="15" t="s">
+        <v>612</v>
+      </c>
+      <c r="B232" s="15" t="s">
         <v>613</v>
       </c>
-      <c r="B232" s="15" t="s">
-        <v>614</v>
-      </c>
       <c r="C232" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D232" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E232" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="B233" s="15" t="s">
         <v>615</v>
       </c>
-      <c r="B233" s="15" t="s">
-        <v>616</v>
-      </c>
       <c r="C233" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D233" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E233" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="B234" s="15" t="s">
         <v>617</v>
       </c>
-      <c r="B234" s="15" t="s">
-        <v>618</v>
-      </c>
       <c r="C234" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D234" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E234" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="B235" s="15" t="s">
         <v>619</v>
       </c>
-      <c r="B235" s="15" t="s">
-        <v>620</v>
-      </c>
       <c r="C235" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D235" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E235" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="15" t="s">
+        <v>620</v>
+      </c>
+      <c r="B236" s="15" t="s">
         <v>621</v>
       </c>
-      <c r="B236" s="15" t="s">
-        <v>622</v>
-      </c>
       <c r="C236" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D236" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E236" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="15" t="s">
+        <v>622</v>
+      </c>
+      <c r="B237" s="15" t="s">
         <v>623</v>
       </c>
-      <c r="B237" s="15" t="s">
-        <v>624</v>
-      </c>
       <c r="C237" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D237" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E237" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="B238" s="15" t="s">
         <v>625</v>
       </c>
-      <c r="B238" s="15" t="s">
-        <v>626</v>
-      </c>
       <c r="C238" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D238" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E238" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="B239" s="15" t="s">
         <v>627</v>
       </c>
-      <c r="B239" s="15" t="s">
-        <v>628</v>
-      </c>
       <c r="C239" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D239" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E239" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="B240" s="15" t="s">
         <v>629</v>
       </c>
-      <c r="B240" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="C240" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D240" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E240" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="B241" s="15" t="s">
         <v>631</v>
       </c>
-      <c r="B241" s="15" t="s">
-        <v>632</v>
-      </c>
       <c r="C241" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D241" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E241" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="B242" s="15" t="s">
         <v>633</v>
       </c>
-      <c r="B242" s="15" t="s">
-        <v>634</v>
-      </c>
       <c r="C242" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D242" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E242" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="B243" s="15" t="s">
         <v>635</v>
       </c>
-      <c r="B243" s="15" t="s">
-        <v>636</v>
-      </c>
       <c r="C243" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D243" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E243" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="15" t="s">
+        <v>636</v>
+      </c>
+      <c r="B244" s="15" t="s">
         <v>637</v>
       </c>
-      <c r="B244" s="15" t="s">
-        <v>638</v>
-      </c>
       <c r="C244" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D244" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E244" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="15" t="s">
+        <v>638</v>
+      </c>
+      <c r="B245" s="15" t="s">
         <v>639</v>
       </c>
-      <c r="B245" s="15" t="s">
-        <v>640</v>
-      </c>
       <c r="C245" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D245" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E245" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="15" t="s">
+        <v>640</v>
+      </c>
+      <c r="B246" s="15" t="s">
         <v>641</v>
       </c>
-      <c r="B246" s="15" t="s">
-        <v>642</v>
-      </c>
       <c r="C246" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D246" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E246" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="B247" s="15" t="s">
         <v>643</v>
       </c>
-      <c r="B247" s="15" t="s">
-        <v>644</v>
-      </c>
       <c r="C247" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D247" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E247" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="B248" s="15" t="s">
         <v>645</v>
       </c>
-      <c r="B248" s="15" t="s">
-        <v>646</v>
-      </c>
       <c r="C248" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D248" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E248" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="B249" s="15" t="s">
         <v>647</v>
       </c>
-      <c r="B249" s="15" t="s">
-        <v>648</v>
-      </c>
       <c r="C249" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D249" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E249" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="B250" s="15" t="s">
         <v>649</v>
       </c>
-      <c r="B250" s="15" t="s">
-        <v>650</v>
-      </c>
       <c r="C250" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D250" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E250" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="B251" s="15" t="s">
         <v>651</v>
       </c>
-      <c r="B251" s="15" t="s">
-        <v>652</v>
-      </c>
       <c r="C251" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D251" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E251" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="B252" s="15" t="s">
         <v>653</v>
       </c>
-      <c r="B252" s="15" t="s">
-        <v>654</v>
-      </c>
       <c r="C252" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D252" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E252" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="B253" s="15" t="s">
         <v>655</v>
       </c>
-      <c r="B253" s="15" t="s">
-        <v>656</v>
-      </c>
       <c r="C253" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D253" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E253" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="B254" s="15" t="s">
         <v>657</v>
       </c>
-      <c r="B254" s="15" t="s">
-        <v>658</v>
-      </c>
       <c r="C254" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D254" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E254" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="B255" s="15" t="s">
         <v>659</v>
       </c>
-      <c r="B255" s="15" t="s">
-        <v>660</v>
-      </c>
       <c r="C255" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D255" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E255" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="B256" s="15" t="s">
         <v>661</v>
       </c>
-      <c r="B256" s="15" t="s">
-        <v>662</v>
-      </c>
       <c r="C256" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D256" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E256" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="B257" s="15" t="s">
         <v>663</v>
       </c>
-      <c r="B257" s="15" t="s">
-        <v>664</v>
-      </c>
       <c r="C257" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D257" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E257" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="B258" s="15" t="s">
         <v>665</v>
       </c>
-      <c r="B258" s="15" t="s">
-        <v>666</v>
-      </c>
       <c r="C258" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D258" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E258" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="15" t="s">
+        <v>666</v>
+      </c>
+      <c r="B259" s="15" t="s">
         <v>667</v>
       </c>
-      <c r="B259" s="15" t="s">
-        <v>668</v>
-      </c>
       <c r="C259" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D259" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E259" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="B260" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="B260" s="15" t="s">
-        <v>670</v>
-      </c>
       <c r="C260" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D260" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E260" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="B261" s="15" t="s">
         <v>671</v>
       </c>
-      <c r="B261" s="15" t="s">
-        <v>672</v>
-      </c>
       <c r="C261" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D261" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E261" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="15" t="s">
+        <v>672</v>
+      </c>
+      <c r="B262" s="15" t="s">
         <v>673</v>
       </c>
-      <c r="B262" s="15" t="s">
-        <v>674</v>
-      </c>
       <c r="C262" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D262" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E262" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="B263" s="15" t="s">
         <v>675</v>
       </c>
-      <c r="B263" s="15" t="s">
-        <v>676</v>
-      </c>
       <c r="C263" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D263" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E263" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="15" t="s">
+        <v>676</v>
+      </c>
+      <c r="B264" s="15" t="s">
         <v>677</v>
       </c>
-      <c r="B264" s="15" t="s">
-        <v>678</v>
-      </c>
       <c r="C264" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D264" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E264" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="15" t="s">
+        <v>678</v>
+      </c>
+      <c r="B265" s="15" t="s">
         <v>679</v>
       </c>
-      <c r="B265" s="15" t="s">
-        <v>680</v>
-      </c>
       <c r="C265" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D265" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E265" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="15" t="s">
+        <v>680</v>
+      </c>
+      <c r="B266" s="15" t="s">
         <v>681</v>
       </c>
-      <c r="B266" s="15" t="s">
-        <v>682</v>
-      </c>
       <c r="C266" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D266" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E266" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="B267" s="15" t="s">
         <v>683</v>
       </c>
-      <c r="B267" s="15" t="s">
-        <v>684</v>
-      </c>
       <c r="C267" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D267" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E267" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="15" t="s">
+        <v>684</v>
+      </c>
+      <c r="B268" s="15" t="s">
         <v>685</v>
       </c>
-      <c r="B268" s="15" t="s">
-        <v>686</v>
-      </c>
       <c r="C268" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D268" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E268" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="B269" s="15" t="s">
         <v>687</v>
       </c>
-      <c r="B269" s="15" t="s">
-        <v>688</v>
-      </c>
       <c r="C269" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D269" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E269" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="B270" s="15" t="s">
         <v>689</v>
       </c>
-      <c r="B270" s="15" t="s">
-        <v>690</v>
-      </c>
       <c r="C270" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D270" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E270" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="15" t="s">
+        <v>690</v>
+      </c>
+      <c r="B271" s="15" t="s">
         <v>691</v>
       </c>
-      <c r="B271" s="15" t="s">
-        <v>692</v>
-      </c>
       <c r="C271" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D271" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E271" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="15" t="s">
+        <v>692</v>
+      </c>
+      <c r="B272" s="15" t="s">
         <v>693</v>
       </c>
-      <c r="B272" s="15" t="s">
-        <v>694</v>
-      </c>
       <c r="C272" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D272" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E272" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="15" t="s">
+        <v>694</v>
+      </c>
+      <c r="B273" s="15" t="s">
         <v>695</v>
       </c>
-      <c r="B273" s="15" t="s">
-        <v>696</v>
-      </c>
       <c r="C273" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D273" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E273" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="15" t="s">
+        <v>696</v>
+      </c>
+      <c r="B274" s="15" t="s">
         <v>697</v>
       </c>
-      <c r="B274" s="15" t="s">
-        <v>698</v>
-      </c>
       <c r="C274" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D274" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E274" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="B275" s="15" t="s">
         <v>699</v>
       </c>
-      <c r="B275" s="15" t="s">
-        <v>700</v>
-      </c>
       <c r="C275" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D275" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E275" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="15" t="s">
+        <v>700</v>
+      </c>
+      <c r="B276" s="15" t="s">
         <v>701</v>
       </c>
-      <c r="B276" s="15" t="s">
-        <v>702</v>
-      </c>
       <c r="C276" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D276" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E276" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="B277" s="15" t="s">
         <v>703</v>
       </c>
-      <c r="B277" s="15" t="s">
-        <v>704</v>
-      </c>
       <c r="C277" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D277" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E277" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="15" t="s">
+        <v>704</v>
+      </c>
+      <c r="B278" s="15" t="s">
         <v>705</v>
       </c>
-      <c r="B278" s="15" t="s">
-        <v>706</v>
-      </c>
       <c r="C278" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D278" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E278" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="B279" s="15" t="s">
         <v>707</v>
       </c>
-      <c r="B279" s="15" t="s">
-        <v>708</v>
-      </c>
       <c r="C279" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D279" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E279" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="15" t="s">
+        <v>708</v>
+      </c>
+      <c r="B280" s="15" t="s">
         <v>709</v>
       </c>
-      <c r="B280" s="15" t="s">
-        <v>710</v>
-      </c>
       <c r="C280" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D280" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E280" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="B281" s="15" t="s">
         <v>711</v>
       </c>
-      <c r="B281" s="15" t="s">
-        <v>712</v>
-      </c>
       <c r="C281" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D281" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E281" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="B282" s="15" t="s">
         <v>713</v>
       </c>
-      <c r="B282" s="15" t="s">
-        <v>714</v>
-      </c>
       <c r="C282" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D282" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E282" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="B283" s="15" t="s">
         <v>715</v>
       </c>
-      <c r="B283" s="15" t="s">
-        <v>716</v>
-      </c>
       <c r="C283" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D283" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E283" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="15" t="s">
+        <v>716</v>
+      </c>
+      <c r="B284" s="15" t="s">
         <v>717</v>
       </c>
-      <c r="B284" s="15" t="s">
-        <v>718</v>
-      </c>
       <c r="C284" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D284" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E284" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="15" t="s">
+        <v>718</v>
+      </c>
+      <c r="B285" s="15" t="s">
         <v>719</v>
       </c>
-      <c r="B285" s="15" t="s">
-        <v>720</v>
-      </c>
       <c r="C285" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D285" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E285" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="15" t="s">
+        <v>720</v>
+      </c>
+      <c r="B286" s="15" t="s">
         <v>721</v>
       </c>
-      <c r="B286" s="15" t="s">
-        <v>722</v>
-      </c>
       <c r="C286" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D286" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E286" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="287" spans="1:5">
       <c r="A287" s="15" t="s">
+        <v>722</v>
+      </c>
+      <c r="B287" s="15" t="s">
         <v>723</v>
       </c>
-      <c r="B287" s="15" t="s">
-        <v>724</v>
-      </c>
       <c r="C287" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D287" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E287" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="15" t="s">
+        <v>724</v>
+      </c>
+      <c r="B288" s="15" t="s">
         <v>725</v>
       </c>
-      <c r="B288" s="15" t="s">
-        <v>726</v>
-      </c>
       <c r="C288" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D288" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E288" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="289" spans="1:5">
       <c r="A289" s="15" t="s">
+        <v>726</v>
+      </c>
+      <c r="B289" s="15" t="s">
         <v>727</v>
       </c>
-      <c r="B289" s="15" t="s">
-        <v>728</v>
-      </c>
       <c r="C289" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D289" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E289" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="290" spans="1:5">
       <c r="A290" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="B290" s="15" t="s">
         <v>729</v>
       </c>
-      <c r="B290" s="15" t="s">
-        <v>730</v>
-      </c>
       <c r="C290" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D290" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E290" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="291" spans="1:5">
       <c r="A291" s="15" t="s">
+        <v>730</v>
+      </c>
+      <c r="B291" s="15" t="s">
         <v>731</v>
       </c>
-      <c r="B291" s="15" t="s">
-        <v>732</v>
-      </c>
       <c r="C291" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D291" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E291" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="292" spans="1:5">
       <c r="A292" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="B292" s="15" t="s">
         <v>733</v>
       </c>
-      <c r="B292" s="15" t="s">
-        <v>734</v>
-      </c>
       <c r="C292" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D292" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E292" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="293" spans="1:5">
       <c r="A293" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="B293" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="B293" s="15" t="s">
-        <v>736</v>
-      </c>
       <c r="C293" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D293" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E293" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="294" spans="1:5">
       <c r="A294" s="15" t="s">
+        <v>736</v>
+      </c>
+      <c r="B294" s="15" t="s">
         <v>737</v>
       </c>
-      <c r="B294" s="15" t="s">
-        <v>738</v>
-      </c>
       <c r="C294" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D294" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E294" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="295" spans="1:5">
       <c r="A295" s="15" t="s">
+        <v>738</v>
+      </c>
+      <c r="B295" s="15" t="s">
         <v>739</v>
       </c>
-      <c r="B295" s="15" t="s">
-        <v>740</v>
-      </c>
       <c r="C295" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D295" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E295" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="296" spans="1:5">
       <c r="A296" s="15" t="s">
+        <v>740</v>
+      </c>
+      <c r="B296" s="15" t="s">
         <v>741</v>
       </c>
-      <c r="B296" s="15" t="s">
-        <v>742</v>
-      </c>
       <c r="C296" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D296" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E296" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="297" spans="1:5">
       <c r="A297" s="15" t="s">
+        <v>742</v>
+      </c>
+      <c r="B297" s="15" t="s">
         <v>743</v>
       </c>
-      <c r="B297" s="15" t="s">
-        <v>744</v>
-      </c>
       <c r="C297" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D297" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E297" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="298" spans="1:5">
       <c r="A298" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="B298" s="15" t="s">
         <v>745</v>
       </c>
-      <c r="B298" s="15" t="s">
-        <v>746</v>
-      </c>
       <c r="C298" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D298" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E298" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="299" spans="1:5">
       <c r="A299" s="15" t="s">
+        <v>746</v>
+      </c>
+      <c r="B299" s="15" t="s">
         <v>747</v>
       </c>
-      <c r="B299" s="15" t="s">
-        <v>748</v>
-      </c>
       <c r="C299" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D299" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E299" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="300" spans="1:5">
       <c r="A300" s="15" t="s">
+        <v>748</v>
+      </c>
+      <c r="B300" s="15" t="s">
         <v>749</v>
       </c>
-      <c r="B300" s="15" t="s">
-        <v>750</v>
-      </c>
       <c r="C300" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D300" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E300" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="301" spans="1:5">
       <c r="A301" s="15" t="s">
+        <v>750</v>
+      </c>
+      <c r="B301" s="15" t="s">
         <v>751</v>
       </c>
-      <c r="B301" s="15" t="s">
-        <v>752</v>
-      </c>
       <c r="C301" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D301" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E301" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="302" spans="1:5">
       <c r="A302" s="15" t="s">
+        <v>752</v>
+      </c>
+      <c r="B302" s="15" t="s">
         <v>753</v>
       </c>
-      <c r="B302" s="15" t="s">
-        <v>754</v>
-      </c>
       <c r="C302" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D302" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E302" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="303" spans="1:5">
       <c r="A303" s="15" t="s">
+        <v>754</v>
+      </c>
+      <c r="B303" s="15" t="s">
         <v>755</v>
       </c>
-      <c r="B303" s="15" t="s">
-        <v>756</v>
-      </c>
       <c r="C303" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D303" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E303" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="304" spans="1:5">
       <c r="A304" s="15" t="s">
+        <v>756</v>
+      </c>
+      <c r="B304" s="15" t="s">
         <v>757</v>
       </c>
-      <c r="B304" s="15" t="s">
-        <v>758</v>
-      </c>
       <c r="C304" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D304" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E304" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="305" spans="1:5">
       <c r="A305" s="15" t="s">
+        <v>758</v>
+      </c>
+      <c r="B305" s="15" t="s">
         <v>759</v>
       </c>
-      <c r="B305" s="15" t="s">
-        <v>760</v>
-      </c>
       <c r="C305" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D305" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E305" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="306" spans="1:5">
       <c r="A306" s="15" t="s">
+        <v>760</v>
+      </c>
+      <c r="B306" s="15" t="s">
         <v>761</v>
       </c>
-      <c r="B306" s="15" t="s">
-        <v>762</v>
-      </c>
       <c r="C306" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D306" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E306" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="307" spans="1:5">
       <c r="A307" s="15" t="s">
+        <v>762</v>
+      </c>
+      <c r="B307" s="15" t="s">
         <v>763</v>
       </c>
-      <c r="B307" s="15" t="s">
-        <v>764</v>
-      </c>
       <c r="C307" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D307" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E307" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="308" spans="1:5">
       <c r="A308" s="15" t="s">
+        <v>764</v>
+      </c>
+      <c r="B308" s="15" t="s">
         <v>765</v>
       </c>
-      <c r="B308" s="15" t="s">
-        <v>766</v>
-      </c>
       <c r="C308" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D308" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E308" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="309" spans="1:5">
       <c r="A309" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="B309" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="B309" s="15" t="s">
-        <v>768</v>
-      </c>
       <c r="C309" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D309" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E309" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="310" spans="1:5">
       <c r="A310" s="15" t="s">
+        <v>768</v>
+      </c>
+      <c r="B310" s="15" t="s">
         <v>769</v>
       </c>
-      <c r="B310" s="15" t="s">
-        <v>770</v>
-      </c>
       <c r="C310" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D310" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E310" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="311" spans="1:5">
       <c r="A311" s="15" t="s">
+        <v>770</v>
+      </c>
+      <c r="B311" s="15" t="s">
         <v>771</v>
       </c>
-      <c r="B311" s="15" t="s">
-        <v>772</v>
-      </c>
       <c r="C311" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D311" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E311" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="312" spans="1:5">
       <c r="A312" s="15" t="s">
+        <v>772</v>
+      </c>
+      <c r="B312" s="15" t="s">
         <v>773</v>
       </c>
-      <c r="B312" s="15" t="s">
-        <v>774</v>
-      </c>
       <c r="C312" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D312" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E312" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="313" spans="1:5">
       <c r="A313" s="15" t="s">
+        <v>774</v>
+      </c>
+      <c r="B313" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="B313" s="15" t="s">
-        <v>776</v>
-      </c>
       <c r="C313" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D313" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E313" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="314" spans="1:5">
       <c r="A314" s="15" t="s">
+        <v>776</v>
+      </c>
+      <c r="B314" s="15" t="s">
         <v>777</v>
       </c>
-      <c r="B314" s="15" t="s">
-        <v>778</v>
-      </c>
       <c r="C314" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D314" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E314" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="315" spans="1:5">
       <c r="A315" s="15" t="s">
+        <v>778</v>
+      </c>
+      <c r="B315" s="15" t="s">
         <v>779</v>
       </c>
-      <c r="B315" s="15" t="s">
-        <v>780</v>
-      </c>
       <c r="C315" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D315" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E315" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="316" spans="1:5">
       <c r="A316" s="15" t="s">
+        <v>780</v>
+      </c>
+      <c r="B316" s="15" t="s">
         <v>781</v>
       </c>
-      <c r="B316" s="15" t="s">
-        <v>782</v>
-      </c>
       <c r="C316" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D316" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E316" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="317" spans="1:5">
       <c r="A317" s="15" t="s">
+        <v>782</v>
+      </c>
+      <c r="B317" s="15" t="s">
         <v>783</v>
       </c>
-      <c r="B317" s="15" t="s">
-        <v>784</v>
-      </c>
       <c r="C317" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D317" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E317" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="318" spans="1:5">
       <c r="A318" s="15" t="s">
+        <v>784</v>
+      </c>
+      <c r="B318" s="15" t="s">
         <v>785</v>
       </c>
-      <c r="B318" s="15" t="s">
-        <v>786</v>
-      </c>
       <c r="C318" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D318" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E318" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="319" spans="1:5">
       <c r="A319" s="15" t="s">
+        <v>786</v>
+      </c>
+      <c r="B319" s="15" t="s">
         <v>787</v>
       </c>
-      <c r="B319" s="15" t="s">
-        <v>788</v>
-      </c>
       <c r="C319" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D319" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E319" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="320" spans="1:5">
       <c r="A320" s="15" t="s">
+        <v>788</v>
+      </c>
+      <c r="B320" s="15" t="s">
         <v>789</v>
       </c>
-      <c r="B320" s="15" t="s">
-        <v>790</v>
-      </c>
       <c r="C320" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D320" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E320" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="321" spans="1:5">
       <c r="A321" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="B321" s="15" t="s">
         <v>791</v>
       </c>
-      <c r="B321" s="15" t="s">
-        <v>792</v>
-      </c>
       <c r="C321" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D321" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E321" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="322" spans="1:5">
       <c r="A322" s="15" t="s">
+        <v>792</v>
+      </c>
+      <c r="B322" s="15" t="s">
         <v>793</v>
       </c>
-      <c r="B322" s="15" t="s">
-        <v>794</v>
-      </c>
       <c r="C322" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D322" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E322" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="323" spans="1:5">
       <c r="A323" s="15" t="s">
+        <v>794</v>
+      </c>
+      <c r="B323" s="15" t="s">
         <v>795</v>
       </c>
-      <c r="B323" s="15" t="s">
-        <v>796</v>
-      </c>
       <c r="C323" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D323" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E323" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="324" spans="1:5">
       <c r="A324" s="15" t="s">
+        <v>796</v>
+      </c>
+      <c r="B324" s="15" t="s">
         <v>797</v>
       </c>
-      <c r="B324" s="15" t="s">
-        <v>798</v>
-      </c>
       <c r="C324" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D324" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E324" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="325" spans="1:5">
       <c r="A325" s="15" t="s">
+        <v>798</v>
+      </c>
+      <c r="B325" s="15" t="s">
         <v>799</v>
       </c>
-      <c r="B325" s="15" t="s">
-        <v>800</v>
-      </c>
       <c r="C325" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D325" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E325" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="326" spans="1:5">
       <c r="A326" s="15" t="s">
+        <v>800</v>
+      </c>
+      <c r="B326" s="15" t="s">
         <v>801</v>
       </c>
-      <c r="B326" s="15" t="s">
-        <v>802</v>
-      </c>
       <c r="C326" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D326" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E326" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="327" spans="1:5">
       <c r="A327" s="15" t="s">
+        <v>802</v>
+      </c>
+      <c r="B327" s="15" t="s">
         <v>803</v>
       </c>
-      <c r="B327" s="15" t="s">
-        <v>804</v>
-      </c>
       <c r="C327" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D327" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E327" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="328" spans="1:5">
       <c r="A328" s="15" t="s">
+        <v>804</v>
+      </c>
+      <c r="B328" s="15" t="s">
         <v>805</v>
       </c>
-      <c r="B328" s="15" t="s">
-        <v>806</v>
-      </c>
       <c r="C328" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D328" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E328" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="329" spans="1:5">
       <c r="A329" s="15" t="s">
+        <v>806</v>
+      </c>
+      <c r="B329" s="15" t="s">
         <v>807</v>
       </c>
-      <c r="B329" s="15" t="s">
-        <v>808</v>
-      </c>
       <c r="C329" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D329" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E329" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="330" spans="1:5">
       <c r="A330" s="15" t="s">
+        <v>808</v>
+      </c>
+      <c r="B330" s="15" t="s">
         <v>809</v>
       </c>
-      <c r="B330" s="15" t="s">
-        <v>810</v>
-      </c>
       <c r="C330" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D330" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E330" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="331" spans="1:5">
       <c r="A331" s="15" t="s">
+        <v>810</v>
+      </c>
+      <c r="B331" s="15" t="s">
         <v>811</v>
       </c>
-      <c r="B331" s="15" t="s">
-        <v>812</v>
-      </c>
       <c r="C331" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D331" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E331" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="332" spans="1:5">
       <c r="A332" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="B332" s="15" t="s">
         <v>813</v>
       </c>
-      <c r="B332" s="15" t="s">
-        <v>814</v>
-      </c>
       <c r="C332" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D332" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E332" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="333" spans="1:5">
       <c r="A333" s="15" t="s">
+        <v>814</v>
+      </c>
+      <c r="B333" s="15" t="s">
         <v>815</v>
       </c>
-      <c r="B333" s="15" t="s">
-        <v>816</v>
-      </c>
       <c r="C333" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D333" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E333" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="334" spans="1:5">
       <c r="A334" s="15" t="s">
+        <v>816</v>
+      </c>
+      <c r="B334" s="15" t="s">
         <v>817</v>
       </c>
-      <c r="B334" s="15" t="s">
-        <v>818</v>
-      </c>
       <c r="C334" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D334" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E334" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="335" spans="1:5">
       <c r="A335" s="15" t="s">
+        <v>818</v>
+      </c>
+      <c r="B335" s="15" t="s">
         <v>819</v>
       </c>
-      <c r="B335" s="15" t="s">
-        <v>820</v>
-      </c>
       <c r="C335" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D335" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E335" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="336" spans="1:5">
       <c r="A336" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="B336" s="15" t="s">
         <v>821</v>
       </c>
-      <c r="B336" s="15" t="s">
-        <v>822</v>
-      </c>
       <c r="C336" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D336" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E336" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="337" spans="1:5">
       <c r="A337" s="15" t="s">
+        <v>822</v>
+      </c>
+      <c r="B337" s="15" t="s">
         <v>823</v>
       </c>
-      <c r="B337" s="15" t="s">
-        <v>824</v>
-      </c>
       <c r="C337" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D337" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E337" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="338" spans="1:5">
       <c r="A338" s="15" t="s">
+        <v>824</v>
+      </c>
+      <c r="B338" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="B338" s="15" t="s">
-        <v>826</v>
-      </c>
       <c r="C338" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D338" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E338" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="339" spans="1:5">
       <c r="A339" s="15" t="s">
+        <v>826</v>
+      </c>
+      <c r="B339" s="15" t="s">
         <v>827</v>
       </c>
-      <c r="B339" s="15" t="s">
-        <v>828</v>
-      </c>
       <c r="C339" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D339" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E339" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="340" spans="1:5">
       <c r="A340" s="15" t="s">
+        <v>828</v>
+      </c>
+      <c r="B340" s="15" t="s">
         <v>829</v>
       </c>
-      <c r="B340" s="15" t="s">
-        <v>830</v>
-      </c>
       <c r="C340" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D340" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E340" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="341" spans="1:5">
       <c r="A341" s="15" t="s">
+        <v>830</v>
+      </c>
+      <c r="B341" s="15" t="s">
         <v>831</v>
       </c>
-      <c r="B341" s="15" t="s">
-        <v>832</v>
-      </c>
       <c r="C341" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D341" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E341" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="342" spans="1:5">
       <c r="A342" s="15" t="s">
+        <v>832</v>
+      </c>
+      <c r="B342" s="15" t="s">
         <v>833</v>
       </c>
-      <c r="B342" s="15" t="s">
-        <v>834</v>
-      </c>
       <c r="C342" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D342" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E342" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="343" spans="1:5">
       <c r="A343" s="15" t="s">
+        <v>834</v>
+      </c>
+      <c r="B343" s="15" t="s">
         <v>835</v>
       </c>
-      <c r="B343" s="15" t="s">
-        <v>836</v>
-      </c>
       <c r="C343" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D343" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E343" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="344" spans="1:5">
       <c r="A344" s="15" t="s">
+        <v>836</v>
+      </c>
+      <c r="B344" s="15" t="s">
         <v>837</v>
       </c>
-      <c r="B344" s="15" t="s">
-        <v>838</v>
-      </c>
       <c r="C344" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D344" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E344" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="345" spans="1:5">
       <c r="A345" s="15" t="s">
+        <v>838</v>
+      </c>
+      <c r="B345" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="B345" s="15" t="s">
-        <v>840</v>
-      </c>
       <c r="C345" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D345" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E345" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="346" spans="1:5">
       <c r="A346" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="B346" s="15" t="s">
         <v>841</v>
       </c>
-      <c r="B346" s="15" t="s">
-        <v>842</v>
-      </c>
       <c r="C346" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D346" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E346" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="347" spans="1:5">
       <c r="A347" s="15" t="s">
+        <v>842</v>
+      </c>
+      <c r="B347" s="15" t="s">
         <v>843</v>
       </c>
-      <c r="B347" s="15" t="s">
-        <v>844</v>
-      </c>
       <c r="C347" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D347" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E347" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="348" spans="1:5">
       <c r="A348" s="15" t="s">
+        <v>844</v>
+      </c>
+      <c r="B348" s="15" t="s">
         <v>845</v>
       </c>
-      <c r="B348" s="15" t="s">
-        <v>846</v>
-      </c>
       <c r="C348" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D348" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E348" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="349" spans="1:5">
       <c r="A349" s="15" t="s">
+        <v>846</v>
+      </c>
+      <c r="B349" s="15" t="s">
         <v>847</v>
       </c>
-      <c r="B349" s="15" t="s">
-        <v>848</v>
-      </c>
       <c r="C349" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D349" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E349" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="350" spans="1:5">
       <c r="A350" s="15" t="s">
+        <v>848</v>
+      </c>
+      <c r="B350" s="15" t="s">
         <v>849</v>
       </c>
-      <c r="B350" s="15" t="s">
-        <v>850</v>
-      </c>
       <c r="C350" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D350" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E350" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="351" spans="1:5">
       <c r="A351" s="15" t="s">
+        <v>850</v>
+      </c>
+      <c r="B351" s="15" t="s">
         <v>851</v>
       </c>
-      <c r="B351" s="15" t="s">
-        <v>852</v>
-      </c>
       <c r="C351" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D351" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E351" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="352" spans="1:5">
       <c r="A352" s="15" t="s">
+        <v>852</v>
+      </c>
+      <c r="B352" s="15" t="s">
         <v>853</v>
       </c>
-      <c r="B352" s="15" t="s">
-        <v>854</v>
-      </c>
       <c r="C352" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D352" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E352" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="353" spans="1:5">
       <c r="A353" s="15" t="s">
+        <v>854</v>
+      </c>
+      <c r="B353" s="15" t="s">
         <v>855</v>
       </c>
-      <c r="B353" s="15" t="s">
-        <v>856</v>
-      </c>
       <c r="C353" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D353" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E353" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="354" spans="1:5">
       <c r="A354" s="15" t="s">
+        <v>856</v>
+      </c>
+      <c r="B354" s="15" t="s">
         <v>857</v>
       </c>
-      <c r="B354" s="15" t="s">
-        <v>858</v>
-      </c>
       <c r="C354" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D354" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E354" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="355" spans="1:5">
       <c r="A355" s="15" t="s">
+        <v>858</v>
+      </c>
+      <c r="B355" s="15" t="s">
         <v>859</v>
       </c>
-      <c r="B355" s="15" t="s">
-        <v>860</v>
-      </c>
       <c r="C355" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D355" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E355" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="356" spans="1:5">
       <c r="A356" s="15" t="s">
+        <v>860</v>
+      </c>
+      <c r="B356" s="15" t="s">
         <v>861</v>
       </c>
-      <c r="B356" s="15" t="s">
-        <v>862</v>
-      </c>
       <c r="C356" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D356" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E356" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="357" spans="1:5">
       <c r="A357" s="15" t="s">
+        <v>862</v>
+      </c>
+      <c r="B357" s="15" t="s">
         <v>863</v>
       </c>
-      <c r="B357" s="15" t="s">
-        <v>864</v>
-      </c>
       <c r="C357" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D357" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E357" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="358" spans="1:5">
       <c r="A358" s="15" t="s">
+        <v>864</v>
+      </c>
+      <c r="B358" s="15" t="s">
         <v>865</v>
       </c>
-      <c r="B358" s="15" t="s">
-        <v>866</v>
-      </c>
       <c r="C358" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D358" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E358" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="359" spans="1:5">
       <c r="A359" s="15" t="s">
+        <v>866</v>
+      </c>
+      <c r="B359" s="15" t="s">
         <v>867</v>
       </c>
-      <c r="B359" s="15" t="s">
-        <v>868</v>
-      </c>
       <c r="C359" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D359" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E359" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="360" spans="1:5">
       <c r="A360" s="15" t="s">
+        <v>868</v>
+      </c>
+      <c r="B360" s="15" t="s">
         <v>869</v>
       </c>
-      <c r="B360" s="15" t="s">
-        <v>870</v>
-      </c>
       <c r="C360" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D360" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E360" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="361" spans="1:5">
       <c r="A361" s="15" t="s">
+        <v>870</v>
+      </c>
+      <c r="B361" s="15" t="s">
         <v>871</v>
       </c>
-      <c r="B361" s="15" t="s">
-        <v>872</v>
-      </c>
       <c r="C361" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D361" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E361" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -11052,14 +11052,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1">
       <c r="A1" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
     </row>
     <row r="2" spans="1:3" ht="32" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
@@ -11082,154 +11082,154 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="15" t="s">
+        <v>873</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>874</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="15" t="s">
         <v>875</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="15" t="s">
+        <v>876</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>877</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="15" t="s">
         <v>878</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="15" t="s">
+        <v>879</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>880</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="15" t="s">
         <v>881</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="15" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="15" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="15" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="15" t="s">
+        <v>888</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>889</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="15" t="s">
+        <v>890</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>891</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="15" t="s">
         <v>892</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="15" t="s">
+        <v>893</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>894</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="15" t="s">
         <v>895</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="15" t="s">
+        <v>896</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>897</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="15" t="s">
+        <v>898</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>899</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="15" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="15" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="15" t="s">
+        <v>902</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="15" t="s">
         <v>904</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="15" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
   </sheetData>
